--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D913F6-8284-41CB-ACC7-2B02AA064671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9B89BC-13CF-408D-A557-8BCB70E161EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -37,15 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="12">
   <si>
     <t>n</t>
   </si>
   <si>
     <t>Computational Time (sec)</t>
-  </si>
-  <si>
-    <t>Overall Time (sec)</t>
   </si>
   <si>
     <t>Num Threads</t>
@@ -69,19 +66,13 @@
     <t>POSIX (Cyclic Partitioning)</t>
   </si>
   <si>
-    <t>POSIX (Dynamic Pool Task)</t>
-  </si>
-  <si>
     <t>Speedup</t>
   </si>
   <si>
     <t>Serial Code (Baseline)</t>
   </si>
   <si>
-    <t>OpenMP</t>
-  </si>
-  <si>
-    <t>OpenMp</t>
+    <t>Open MP</t>
   </si>
 </sst>
 </file>
@@ -97,41 +88,35 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -141,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -150,30 +135,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -456,1215 +434,1478 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" style="10" customWidth="1"/>
-    <col min="5" max="6" width="22.6640625" customWidth="1"/>
-    <col min="8" max="8" width="22.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6328125" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22.6328125" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="D1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D3" s="8"/>
+      <c r="E3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>2</v>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="6">
         <v>4.221819</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="10">
+      <c r="C5">
         <v>0.66401900000000003</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5:D35" si="0">B5/C5</f>
+        <v>6.3579792144501885</v>
+      </c>
+      <c r="E5">
+        <v>0.39406000000000002</v>
+      </c>
       <c r="F5">
-        <f>B5/D5</f>
-        <v>6.3579792144501885</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <f>B5/E5</f>
+        <v>10.71364513018322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="6">
         <v>4.7456699999999996</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="10">
+      <c r="C6">
         <v>0.76085100000000006</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="D6" s="6">
+        <f t="shared" si="0"/>
+        <v>6.2373184762851057</v>
+      </c>
+      <c r="E6">
+        <v>0.44486100000000001</v>
+      </c>
       <c r="F6">
-        <f t="shared" ref="F6:F35" si="0">B6/D6</f>
-        <v>6.2373184762851057</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" ref="F6:F35" si="1">B6/E6</f>
+        <v>10.667759142743463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="6">
         <v>5.4632949999999996</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="10">
+      <c r="C7">
         <v>0.84793499999999999</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="D7" s="6">
+        <f t="shared" si="0"/>
+        <v>6.4430587250201956</v>
+      </c>
+      <c r="E7">
+        <v>0.503745</v>
+      </c>
       <c r="F7">
-        <f t="shared" si="0"/>
-        <v>6.4430587250201956</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10.84535826658329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="6">
         <v>6.0686730000000004</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="10">
+      <c r="C8">
         <v>0.93635000000000002</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="D8" s="6">
+        <f t="shared" si="0"/>
+        <v>6.4812014738078716</v>
+      </c>
+      <c r="E8">
+        <v>0.56333999999999995</v>
+      </c>
       <c r="F8">
-        <f t="shared" si="0"/>
-        <v>6.4812014738078716</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10.77266482053467</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="6">
         <v>6.7864820000000003</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="10">
+      <c r="C9">
         <v>1.0725750000000001</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="D9" s="6">
+        <f t="shared" si="0"/>
+        <v>6.3272796774118358</v>
+      </c>
+      <c r="E9">
+        <v>0.64324000000000003</v>
+      </c>
       <c r="F9">
-        <f t="shared" si="0"/>
-        <v>6.3272796774118358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10.550466388906163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="6">
         <v>7.5130920000000003</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="10">
+      <c r="C10">
         <v>1.16066</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="D10" s="6">
+        <f t="shared" si="0"/>
+        <v>6.4731204659417916</v>
+      </c>
+      <c r="E10">
+        <v>0.71464700000000003</v>
+      </c>
       <c r="F10">
-        <f t="shared" si="0"/>
-        <v>6.4731204659417916</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10.513011318874913</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="6">
         <v>8.2434170000000009</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="10">
+      <c r="C11">
         <v>1.268275</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="D11" s="6">
+        <f t="shared" si="0"/>
+        <v>6.4997078709270468</v>
+      </c>
+      <c r="E11">
+        <v>0.76313900000000001</v>
+      </c>
       <c r="F11">
-        <f t="shared" si="0"/>
-        <v>6.4997078709270468</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10.801986269866958</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="6">
         <v>9.0389809999999997</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="10">
+      <c r="C12">
         <v>1.3796630000000001</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="D12" s="6">
+        <f t="shared" si="0"/>
+        <v>6.5515861482115554</v>
+      </c>
+      <c r="E12">
+        <v>0.83806499999999995</v>
+      </c>
       <c r="F12">
-        <f t="shared" si="0"/>
-        <v>6.5515861482115554</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>10.785536921360515</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="6">
         <v>11.076497</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="10">
+      <c r="C13">
         <v>1.566074</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="D13" s="6">
+        <f t="shared" si="0"/>
+        <v>7.0727800857430747</v>
+      </c>
+      <c r="E13">
+        <v>0.91649099999999994</v>
+      </c>
       <c r="F13">
-        <f t="shared" si="0"/>
-        <v>7.0727800857430747</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>12.085767345233069</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="6">
         <v>11.668153999999999</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="10">
+      <c r="C14">
         <v>1.6360399999999999</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="D14" s="6">
+        <f t="shared" si="0"/>
+        <v>7.1319490965991053</v>
+      </c>
+      <c r="E14">
+        <v>0.96938500000000005</v>
+      </c>
       <c r="F14">
-        <f t="shared" si="0"/>
-        <v>7.1319490965991053</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>12.036656230496654</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="6">
         <v>12.374013</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="10">
+      <c r="C15">
         <v>1.75071</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="D15" s="6">
+        <f t="shared" si="0"/>
+        <v>7.0679969840807439</v>
+      </c>
+      <c r="E15">
+        <v>1.0389330000000001</v>
+      </c>
       <c r="F15">
-        <f t="shared" si="0"/>
-        <v>7.0679969840807439</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.910308941962569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="6">
         <v>13.410712999999999</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="10">
+      <c r="C16">
         <v>1.9254990000000001</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="D16" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9647987352888778</v>
+      </c>
+      <c r="E16">
+        <v>1.1112550000000001</v>
+      </c>
       <c r="F16">
-        <f t="shared" si="0"/>
-        <v>6.9647987352888778</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>12.068078883784548</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="6">
         <v>13.503204</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="10">
+      <c r="C17">
         <v>2.0128330000000001</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="D17" s="6">
+        <f t="shared" si="0"/>
+        <v>6.708556546916709</v>
+      </c>
+      <c r="E17">
+        <v>1.20808</v>
+      </c>
       <c r="F17">
-        <f t="shared" si="0"/>
-        <v>6.708556546916709</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.177408780875439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="6">
         <v>15.334875</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="10">
+      <c r="C18">
         <v>2.1030869999999999</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="D18" s="6">
+        <f t="shared" si="0"/>
+        <v>7.2916027724958603</v>
+      </c>
+      <c r="E18">
+        <v>1.270966</v>
+      </c>
       <c r="F18">
-        <f t="shared" si="0"/>
-        <v>7.2916027724958603</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>12.06552732331156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="6">
         <v>15.795399</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="10">
+      <c r="C19">
         <v>2.2671899999999998</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="D19" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9669498365818487</v>
+      </c>
+      <c r="E19">
+        <v>1.353019</v>
+      </c>
       <c r="F19">
-        <f t="shared" si="0"/>
-        <v>6.9669498365818487</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.674188610802952</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="6">
         <v>17.032720999999999</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="10">
+      <c r="C20">
         <v>2.413516</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="D20" s="6">
+        <f t="shared" si="0"/>
+        <v>7.0572231549324718</v>
+      </c>
+      <c r="E20">
+        <v>1.428434</v>
+      </c>
       <c r="F20">
-        <f t="shared" si="0"/>
-        <v>7.0572231549324718</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.924051793782562</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="6">
         <v>18.229096999999999</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="10">
+      <c r="C21">
         <v>2.524848</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="D21" s="6">
+        <f t="shared" si="0"/>
+        <v>7.2198789788533801</v>
+      </c>
+      <c r="E21">
+        <v>1.5375620000000001</v>
+      </c>
       <c r="F21">
-        <f t="shared" si="0"/>
-        <v>7.2198789788533801</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.855845162666609</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="6">
         <v>19.070878</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="10">
+      <c r="C22">
         <v>2.716825</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="D22" s="6">
+        <f t="shared" si="0"/>
+        <v>7.0195459773816866</v>
+      </c>
+      <c r="E22">
+        <v>1.596641</v>
+      </c>
       <c r="F22">
-        <f t="shared" si="0"/>
-        <v>7.0195459773816866</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.944374471155383</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="6">
         <v>20.289345000000001</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="10">
+      <c r="C23">
         <v>2.8388429999999998</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="D23" s="6">
+        <f t="shared" si="0"/>
+        <v>7.1470472301567938</v>
+      </c>
+      <c r="E23">
+        <v>1.672161</v>
+      </c>
       <c r="F23">
-        <f t="shared" si="0"/>
-        <v>7.1470472301567938</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>12.133607350009958</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="6">
         <v>20.676687000000001</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="10">
+      <c r="C24">
         <v>2.9750390000000002</v>
       </c>
-      <c r="E24" s="7"/>
+      <c r="D24" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9500557807813612</v>
+      </c>
+      <c r="E24">
+        <v>1.7628299999999999</v>
+      </c>
       <c r="F24">
-        <f t="shared" si="0"/>
-        <v>6.9500557807813612</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.72925750072327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="6">
         <v>21.899799999999999</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="10">
+      <c r="C25">
         <v>3.0683389999999999</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="D25" s="6">
+        <f t="shared" si="0"/>
+        <v>7.1373469489518593</v>
+      </c>
+      <c r="E25">
+        <v>1.8428850000000001</v>
+      </c>
       <c r="F25">
-        <f t="shared" si="0"/>
-        <v>7.1373469489518593</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.88343276981472</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="6">
         <v>22.377856999999999</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="10">
+      <c r="C26">
         <v>3.2272479999999999</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="D26" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9340369875510026</v>
+      </c>
+      <c r="E26">
+        <v>1.928795</v>
+      </c>
       <c r="F26">
-        <f t="shared" si="0"/>
-        <v>6.9340369875510026</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.601988288024387</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="6">
         <v>24.132621</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="10">
+      <c r="C27">
         <v>3.381545</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="D27" s="6">
+        <f t="shared" si="0"/>
+        <v>7.1365665694231479</v>
+      </c>
+      <c r="E27">
+        <v>2.0565920000000002</v>
+      </c>
       <c r="F27">
-        <f t="shared" si="0"/>
-        <v>7.1365665694231479</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.734277387055867</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="6">
         <v>24.831582999999998</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="10">
+      <c r="C28">
         <v>3.4923199999999999</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="D28" s="6">
+        <f t="shared" si="0"/>
+        <v>7.1103401177440784</v>
+      </c>
+      <c r="E28">
+        <v>2.119332</v>
+      </c>
       <c r="F28">
-        <f t="shared" si="0"/>
-        <v>7.1103401177440784</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.716702715761381</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="6">
         <v>26.061553</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="10">
+      <c r="C29">
         <v>3.6668919999999998</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="D29" s="6">
+        <f t="shared" si="0"/>
+        <v>7.1072594993253144</v>
+      </c>
+      <c r="E29">
+        <v>2.2130070000000002</v>
+      </c>
       <c r="F29">
-        <f t="shared" si="0"/>
-        <v>7.1072594993253144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.776534371558697</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="6">
         <v>27.901105000000001</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="10">
+      <c r="C30">
         <v>3.7689819999999998</v>
       </c>
-      <c r="E30" s="7"/>
+      <c r="D30" s="6">
+        <f t="shared" si="0"/>
+        <v>7.4028225658811859</v>
+      </c>
+      <c r="E30">
+        <v>2.3499059999999998</v>
+      </c>
       <c r="F30">
-        <f t="shared" si="0"/>
-        <v>7.4028225658811859</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.873285569720663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="6">
         <v>28.604783999999999</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="10">
+      <c r="C31">
         <v>4.518008</v>
       </c>
-      <c r="E31" s="7"/>
+      <c r="D31" s="6">
+        <f t="shared" si="0"/>
+        <v>6.3312822819260166</v>
+      </c>
+      <c r="E31">
+        <v>2.4693049999999999</v>
+      </c>
       <c r="F31">
-        <f t="shared" si="0"/>
-        <v>6.3312822819260166</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>11.584143716551823</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="6">
         <v>29.860191</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="10">
+      <c r="C32">
         <v>5.2665649999999999</v>
       </c>
-      <c r="E32" s="7"/>
+      <c r="D32" s="6">
+        <f t="shared" si="0"/>
+        <v>5.6697659670012621</v>
+      </c>
+      <c r="E32">
+        <v>3.0958739999999998</v>
+      </c>
       <c r="F32">
-        <f t="shared" si="0"/>
-        <v>5.6697659670012621</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>9.6451570703458867</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="6">
         <v>30.595779</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="10">
+      <c r="C33">
         <v>4.8746859999999996</v>
       </c>
-      <c r="E33" s="7"/>
+      <c r="D33" s="6">
+        <f t="shared" si="0"/>
+        <v>6.276461499263748</v>
+      </c>
+      <c r="E33">
+        <v>3.0987979999999999</v>
+      </c>
       <c r="F33">
-        <f t="shared" si="0"/>
-        <v>6.276461499263748</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>9.8734344736249344</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="6">
         <v>30.810445000000001</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="10">
+      <c r="C34">
         <v>4.905627</v>
       </c>
-      <c r="E34" s="7"/>
+      <c r="D34" s="6">
+        <f t="shared" si="0"/>
+        <v>6.2806334440021638</v>
+      </c>
+      <c r="E34">
+        <v>3.2922889999999998</v>
+      </c>
       <c r="F34">
-        <f t="shared" si="0"/>
-        <v>6.2806334440021638</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>9.3583658664230285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="6">
         <v>32.276363000000003</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="10">
+      <c r="C35">
         <v>5.2940889999999996</v>
       </c>
-      <c r="E35" s="7"/>
+      <c r="D35" s="6">
+        <f t="shared" si="0"/>
+        <v>6.0966793342537322</v>
+      </c>
+      <c r="E35">
+        <v>3.4938380000000002</v>
+      </c>
       <c r="F35">
-        <f t="shared" si="0"/>
-        <v>6.0966793342537322</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B38" s="13" t="s">
+        <f t="shared" si="1"/>
+        <v>9.2380823037587891</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B36"/>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D38" s="8"/>
+      <c r="E38" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D39" s="9" t="s">
+      <c r="C39" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>2</v>
+      <c r="D39" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="6">
         <v>3.07422</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="10">
+      <c r="C40">
         <v>0.19961499999999999</v>
       </c>
-      <c r="E40" s="7"/>
+      <c r="D40" s="6">
+        <f t="shared" ref="D40:D70" si="2">B40/C40</f>
+        <v>15.400746436891016</v>
+      </c>
+      <c r="E40">
+        <v>0.216973</v>
+      </c>
       <c r="F40">
-        <f>B40/D40</f>
-        <v>15.400746436891016</v>
-      </c>
-      <c r="H40" s="10">
-        <v>0.216973</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <f>B40/E40</f>
+        <v>14.168675365137597</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="6">
         <v>4.0935550000000003</v>
       </c>
-      <c r="D41" s="10">
+      <c r="C41">
         <v>0.208622</v>
       </c>
+      <c r="D41" s="6">
+        <f t="shared" si="2"/>
+        <v>19.621875928713177</v>
+      </c>
+      <c r="E41">
+        <v>0.21165</v>
+      </c>
       <c r="F41">
-        <f>B41/D41</f>
-        <v>19.621875928713177</v>
-      </c>
-      <c r="H41" s="10">
-        <v>0.21165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" ref="F41:F70" si="3">B41/E41</f>
+        <v>19.341152846680842</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="6">
         <v>4.904312</v>
       </c>
-      <c r="D42" s="10">
+      <c r="C42">
         <v>0.230629</v>
       </c>
+      <c r="D42" s="6">
+        <f t="shared" si="2"/>
+        <v>21.264940662275777</v>
+      </c>
+      <c r="E42">
+        <v>0.245451</v>
+      </c>
       <c r="F42">
-        <f t="shared" ref="F42:F69" si="1">B42/D42</f>
-        <v>21.264940662275777</v>
-      </c>
-      <c r="H42" s="10">
-        <v>0.245451</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>19.980818982200113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="6">
         <v>5.4954840000000003</v>
       </c>
-      <c r="D43" s="10">
+      <c r="C43">
         <v>0.268316</v>
       </c>
+      <c r="D43" s="6">
+        <f t="shared" si="2"/>
+        <v>20.481387617585238</v>
+      </c>
+      <c r="E43">
+        <v>0.25640299999999999</v>
+      </c>
       <c r="F43">
-        <f t="shared" si="1"/>
-        <v>20.481387617585238</v>
-      </c>
-      <c r="H43" s="10">
-        <v>0.25640299999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.432994153734551</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="6">
         <v>6.1328820000000004</v>
       </c>
-      <c r="D44" s="10">
+      <c r="C44">
         <v>0.29424</v>
       </c>
+      <c r="D44" s="6">
+        <f t="shared" si="2"/>
+        <v>20.843128058727572</v>
+      </c>
+      <c r="E44">
+        <v>0.28809899999999999</v>
+      </c>
       <c r="F44">
-        <f t="shared" si="1"/>
-        <v>20.843128058727572</v>
-      </c>
-      <c r="H44" s="10">
-        <v>0.28809899999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.287411618922665</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="6">
         <v>6.7988749999999998</v>
       </c>
-      <c r="D45" s="10">
+      <c r="C45">
         <v>0.319859</v>
       </c>
+      <c r="D45" s="6">
+        <f t="shared" si="2"/>
+        <v>21.255850234009358</v>
+      </c>
+      <c r="E45">
+        <v>0.329737</v>
+      </c>
       <c r="F45">
-        <f t="shared" si="1"/>
-        <v>21.255850234009358</v>
-      </c>
-      <c r="H45" s="10">
-        <v>0.329737</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>20.619084300518292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="6">
         <v>7.4492789999999998</v>
       </c>
-      <c r="D46" s="10">
+      <c r="C46">
         <v>0.374307</v>
       </c>
+      <c r="D46" s="6">
+        <f t="shared" si="2"/>
+        <v>19.901522012679433</v>
+      </c>
+      <c r="E46">
+        <v>0.34054099999999998</v>
+      </c>
       <c r="F46">
-        <f t="shared" si="1"/>
-        <v>19.901522012679433</v>
-      </c>
-      <c r="H46" s="10">
-        <v>0.34054099999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.874837391092409</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="6">
         <v>7.9789300000000001</v>
       </c>
-      <c r="D47" s="10">
+      <c r="C47">
         <v>0.41203099999999998</v>
       </c>
+      <c r="D47" s="6">
+        <f t="shared" si="2"/>
+        <v>19.364877885401828</v>
+      </c>
+      <c r="E47">
+        <v>0.37627100000000002</v>
+      </c>
       <c r="F47">
-        <f t="shared" si="1"/>
-        <v>19.364877885401828</v>
-      </c>
-      <c r="H47" s="10">
-        <v>0.37627100000000002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.205274921532617</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="6">
         <v>8.7212800000000001</v>
       </c>
-      <c r="D48" s="10">
+      <c r="C48">
         <v>0.39272200000000002</v>
       </c>
+      <c r="D48" s="6">
+        <f t="shared" si="2"/>
+        <v>22.207261116005725</v>
+      </c>
+      <c r="E48">
+        <v>0.39349200000000001</v>
+      </c>
       <c r="F48">
-        <f t="shared" si="1"/>
-        <v>22.207261116005725</v>
-      </c>
-      <c r="H48" s="10">
-        <v>0.39349200000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.163805109125473</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="6">
         <v>9.3753119999999992</v>
       </c>
-      <c r="D49" s="10">
+      <c r="C49">
         <v>0.41116200000000003</v>
       </c>
+      <c r="D49" s="6">
+        <f t="shared" si="2"/>
+        <v>22.801990456316485</v>
+      </c>
+      <c r="E49">
+        <v>0.42541000000000001</v>
+      </c>
       <c r="F49">
-        <f t="shared" si="1"/>
-        <v>22.801990456316485</v>
-      </c>
-      <c r="H49" s="10">
-        <v>0.42541000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.038297172139817</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="6">
         <v>10.080152999999999</v>
       </c>
-      <c r="D50" s="10">
+      <c r="C50">
         <v>0.46141599999999999</v>
       </c>
+      <c r="D50" s="6">
+        <f t="shared" si="2"/>
+        <v>21.846128005964246</v>
+      </c>
+      <c r="E50">
+        <v>0.44863900000000001</v>
+      </c>
       <c r="F50">
-        <f t="shared" si="1"/>
-        <v>21.846128005964246</v>
-      </c>
-      <c r="H50" s="10">
-        <v>0.44863900000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.46829410728893</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="6">
         <v>10.752592999999999</v>
       </c>
-      <c r="D51" s="10">
+      <c r="C51">
         <v>0.64751300000000001</v>
       </c>
+      <c r="D51" s="6">
+        <f t="shared" si="2"/>
+        <v>16.605987833448904</v>
+      </c>
+      <c r="E51">
+        <v>0.459978</v>
+      </c>
       <c r="F51">
-        <f t="shared" si="1"/>
-        <v>16.605987833448904</v>
-      </c>
-      <c r="H51" s="10">
-        <v>0.459978</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.376320171834305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="6">
         <v>11.561036</v>
       </c>
-      <c r="D52" s="10">
+      <c r="C52">
         <v>0.73573200000000005</v>
       </c>
+      <c r="D52" s="6">
+        <f t="shared" si="2"/>
+        <v>15.71365116645735</v>
+      </c>
+      <c r="E52">
+        <v>0.50284499999999999</v>
+      </c>
       <c r="F52">
-        <f t="shared" si="1"/>
-        <v>15.71365116645735</v>
-      </c>
-      <c r="H52" s="10">
-        <v>0.50284499999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.991251777386669</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="6">
         <v>12.216346</v>
       </c>
-      <c r="D53" s="10">
+      <c r="C53">
         <v>0.65195899999999996</v>
       </c>
+      <c r="D53" s="6">
+        <f t="shared" si="2"/>
+        <v>18.737905297725778</v>
+      </c>
+      <c r="E53">
+        <v>0.53020299999999998</v>
+      </c>
       <c r="F53">
-        <f t="shared" si="1"/>
-        <v>18.737905297725778</v>
-      </c>
-      <c r="H53" s="10">
-        <v>0.53020299999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.040884340526176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="6">
         <v>13.036834000000001</v>
       </c>
-      <c r="D54" s="10">
+      <c r="C54">
         <v>0.62831400000000004</v>
       </c>
+      <c r="D54" s="6">
+        <f t="shared" si="2"/>
+        <v>20.748915351241575</v>
+      </c>
+      <c r="E54">
+        <v>0.55043200000000003</v>
+      </c>
       <c r="F54">
-        <f t="shared" si="1"/>
-        <v>20.748915351241575</v>
-      </c>
-      <c r="H54" s="10">
-        <v>0.55043200000000003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.684731265624091</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="6">
         <v>13.817802</v>
       </c>
-      <c r="D55" s="10">
+      <c r="C55">
         <v>0.62590500000000004</v>
       </c>
+      <c r="D55" s="6">
+        <f t="shared" si="2"/>
+        <v>22.07651640424665</v>
+      </c>
+      <c r="E55">
+        <v>0.60006199999999998</v>
+      </c>
       <c r="F55">
-        <f t="shared" si="1"/>
-        <v>22.07651640424665</v>
-      </c>
-      <c r="H55" s="10">
-        <v>0.60006199999999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.027290513313627</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="6">
         <v>14.610976000000001</v>
       </c>
-      <c r="D56" s="10">
+      <c r="C56">
         <v>0.64108600000000004</v>
       </c>
+      <c r="D56" s="6">
+        <f t="shared" si="2"/>
+        <v>22.790976561646954</v>
+      </c>
+      <c r="E56">
+        <v>0.68986199999999998</v>
+      </c>
       <c r="F56">
-        <f t="shared" si="1"/>
-        <v>22.790976561646954</v>
-      </c>
-      <c r="H56" s="10">
-        <v>0.68986199999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.17956344892167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="6">
         <v>15.201309999999999</v>
       </c>
-      <c r="D57" s="10">
+      <c r="C57">
         <v>0.68704200000000004</v>
       </c>
+      <c r="D57" s="6">
+        <f t="shared" si="2"/>
+        <v>22.125736126757896</v>
+      </c>
+      <c r="E57">
+        <v>0.64302199999999998</v>
+      </c>
       <c r="F57">
-        <f t="shared" si="1"/>
-        <v>22.125736126757896</v>
-      </c>
-      <c r="H57" s="10">
-        <v>0.64302199999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.640419767908408</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="6">
         <v>16.062538</v>
       </c>
-      <c r="D58" s="10">
+      <c r="C58">
         <v>0.85647399999999996</v>
       </c>
+      <c r="D58" s="6">
+        <f t="shared" si="2"/>
+        <v>18.754262242636671</v>
+      </c>
+      <c r="E58">
+        <v>0.71674599999999999</v>
+      </c>
       <c r="F58">
-        <f t="shared" si="1"/>
-        <v>18.754262242636671</v>
-      </c>
-      <c r="H58" s="10">
-        <v>0.71674599999999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.410362945869249</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="6">
         <v>16.927885</v>
       </c>
-      <c r="D59" s="10">
+      <c r="C59">
         <v>0.87755899999999998</v>
       </c>
+      <c r="D59" s="6">
+        <f t="shared" si="2"/>
+        <v>19.289740063061288</v>
+      </c>
+      <c r="E59">
+        <v>0.73519000000000001</v>
+      </c>
       <c r="F59">
-        <f t="shared" si="1"/>
-        <v>19.289740063061288</v>
-      </c>
-      <c r="H59" s="10">
-        <v>0.73519000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.025183966049592</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="6">
         <v>17.821466000000001</v>
       </c>
-      <c r="D60" s="10">
+      <c r="C60">
         <v>0.91805499999999995</v>
       </c>
+      <c r="D60" s="6">
+        <f t="shared" si="2"/>
+        <v>19.412198615551358</v>
+      </c>
+      <c r="E60">
+        <v>0.89686399999999999</v>
+      </c>
       <c r="F60">
-        <f t="shared" si="1"/>
-        <v>19.412198615551358</v>
-      </c>
-      <c r="H60" s="10">
-        <v>0.89686399999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>19.870867823884112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="6">
         <v>18.579981</v>
       </c>
-      <c r="D61" s="10">
+      <c r="C61">
         <v>0.94625599999999999</v>
       </c>
+      <c r="D61" s="6">
+        <f t="shared" si="2"/>
+        <v>19.635258323328994</v>
+      </c>
+      <c r="E61">
+        <v>0.85248999999999997</v>
+      </c>
       <c r="F61">
-        <f t="shared" si="1"/>
-        <v>19.635258323328994</v>
-      </c>
-      <c r="H61" s="10">
-        <v>0.85248999999999997</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.794954779528208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="6">
         <v>19.452786</v>
       </c>
-      <c r="D62" s="10">
+      <c r="C62">
         <v>0.89138200000000001</v>
       </c>
+      <c r="D62" s="6">
+        <f t="shared" si="2"/>
+        <v>21.823175697961144</v>
+      </c>
+      <c r="E62">
+        <v>0.96400200000000003</v>
+      </c>
       <c r="F62">
-        <f t="shared" si="1"/>
-        <v>21.823175697961144</v>
-      </c>
-      <c r="H62" s="10">
-        <v>0.96400200000000003</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>20.179196723658247</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="6">
         <v>20.361827999999999</v>
       </c>
-      <c r="D63" s="10">
+      <c r="C63">
         <v>1.0145040000000001</v>
       </c>
+      <c r="D63" s="6">
+        <f t="shared" si="2"/>
+        <v>20.070722244564831</v>
+      </c>
+      <c r="E63">
+        <v>0.87285800000000002</v>
+      </c>
       <c r="F63">
-        <f t="shared" si="1"/>
-        <v>20.070722244564831</v>
-      </c>
-      <c r="H63" s="10">
-        <v>0.87285800000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.327766944909708</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="6">
         <v>21.225096000000001</v>
       </c>
-      <c r="D64" s="10">
+      <c r="C64">
         <v>1.081969</v>
       </c>
+      <c r="D64" s="6">
+        <f t="shared" si="2"/>
+        <v>19.617101783877359</v>
+      </c>
+      <c r="E64">
+        <v>0.89015500000000003</v>
+      </c>
       <c r="F64">
-        <f t="shared" si="1"/>
-        <v>19.617101783877359</v>
-      </c>
-      <c r="H64" s="10">
-        <v>0.89015500000000003</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.844269818177732</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="6">
         <v>22.179998999999999</v>
       </c>
-      <c r="D65" s="10">
+      <c r="C65">
         <v>1.1624030000000001</v>
       </c>
+      <c r="D65" s="6">
+        <f t="shared" si="2"/>
+        <v>19.081161180760887</v>
+      </c>
+      <c r="E65">
+        <v>0.985043</v>
+      </c>
       <c r="F65">
-        <f t="shared" si="1"/>
-        <v>19.081161180760887</v>
-      </c>
-      <c r="H65" s="10">
-        <v>0.985043</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.516782516093205</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="6">
         <v>23.211036</v>
       </c>
-      <c r="D66" s="10">
+      <c r="C66">
         <v>1.1323209999999999</v>
       </c>
+      <c r="D66" s="6">
+        <f t="shared" si="2"/>
+        <v>20.498635987498247</v>
+      </c>
+      <c r="E66">
+        <v>1.027749</v>
+      </c>
       <c r="F66">
-        <f t="shared" si="1"/>
-        <v>20.498635987498247</v>
-      </c>
-      <c r="H66" s="10">
-        <v>1.027749</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>22.584343064308502</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="6">
         <v>23.925511</v>
       </c>
-      <c r="D67" s="10">
+      <c r="C67">
         <v>1.200993</v>
       </c>
+      <c r="D67" s="6">
+        <f t="shared" si="2"/>
+        <v>19.921440841037377</v>
+      </c>
+      <c r="E67">
+        <v>1.011207</v>
+      </c>
       <c r="F67">
-        <f>B67/D67</f>
-        <v>19.921440841037377</v>
-      </c>
-      <c r="H67" s="10">
-        <v>1.011207</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>23.660349463561865</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="6">
         <v>24.83474</v>
       </c>
-      <c r="D68" s="10">
+      <c r="C68">
         <v>1.212243</v>
       </c>
+      <c r="D68" s="6">
+        <f t="shared" si="2"/>
+        <v>20.486602108653134</v>
+      </c>
+      <c r="E68">
+        <v>1.143842</v>
+      </c>
       <c r="F68">
-        <f t="shared" si="1"/>
-        <v>20.486602108653134</v>
-      </c>
-      <c r="H68" s="10">
-        <v>1.143842</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>21.711687453337085</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="6">
         <v>25.810836999999999</v>
       </c>
-      <c r="D69" s="10">
+      <c r="C69">
         <v>1.2506710000000001</v>
       </c>
+      <c r="D69" s="6">
+        <f t="shared" si="2"/>
+        <v>20.637591340968168</v>
+      </c>
+      <c r="E69">
+        <v>1.156982</v>
+      </c>
       <c r="F69">
-        <f t="shared" si="1"/>
-        <v>20.637591340968168</v>
-      </c>
-      <c r="H69" s="10">
-        <v>1.156982</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="11">
+        <f t="shared" si="3"/>
+        <v>22.308762798384073</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
         <v>40000000</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="6">
         <v>26.719480000000001</v>
       </c>
-      <c r="D70" s="12">
+      <c r="C70">
         <v>1.263007</v>
       </c>
-      <c r="F70" s="12">
-        <f>B70/D70</f>
+      <c r="D70" s="6">
+        <f t="shared" si="2"/>
         <v>21.155448861328562</v>
       </c>
-      <c r="H70" s="12">
+      <c r="E70">
         <v>1.105423</v>
       </c>
+      <c r="F70">
+        <f t="shared" si="3"/>
+        <v>24.171271992712292</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A37:K37"/>
+  <mergeCells count="5">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1672,404 +1913,295 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+    <col min="1" max="4" width="22.6328125" customWidth="1"/>
+    <col min="5" max="5" width="22.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="15" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="6">
         <v>4.221819</v>
       </c>
       <c r="C5">
         <v>1.9988060000000001</v>
       </c>
-      <c r="D5">
-        <v>7.4344469999999996</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="6">
         <f>B5/C5</f>
         <v>2.1121704657680636</v>
       </c>
-      <c r="F5" s="5">
-        <v>2.1946720000000002</v>
-      </c>
-      <c r="G5" s="5">
-        <v>7.352087</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>2.0506150000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <v>4.221819</v>
       </c>
       <c r="C6">
         <v>1.163114</v>
       </c>
-      <c r="D6">
-        <v>6.4049259999999997</v>
+      <c r="D6" s="6">
+        <f t="shared" ref="D6:D10" si="0">B6/C6</f>
+        <v>3.6297551228856331</v>
       </c>
       <c r="E6">
-        <f t="shared" ref="E6:E10" si="0">B6/C6</f>
-        <v>3.6297551228856331</v>
-      </c>
-      <c r="F6" s="5">
-        <v>1.1574359999999999</v>
-      </c>
-      <c r="G6" s="5">
-        <v>6.3732189999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.62085500000000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
         <v>4.221819</v>
       </c>
       <c r="C7">
         <v>0.66360600000000003</v>
       </c>
-      <c r="D7">
-        <v>6.0478170000000002</v>
+      <c r="D7" s="6">
+        <f t="shared" si="0"/>
+        <v>6.3619361488594128</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>6.3619361488594128</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1.4256819999999999</v>
-      </c>
-      <c r="G7" s="5">
-        <v>6.6873300000000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.39751399999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>16</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="6">
         <v>4.221819</v>
       </c>
       <c r="C8">
         <v>0.445718</v>
       </c>
-      <c r="D8">
-        <v>5.636774</v>
+      <c r="D8" s="6">
+        <f t="shared" si="0"/>
+        <v>9.4719508747683516</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>9.4719508747683516</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1.4419729999999999</v>
-      </c>
-      <c r="G8" s="5">
-        <v>6.7687369999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.39396199999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>32</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
         <v>4.221819</v>
       </c>
       <c r="C9">
         <v>0.44677899999999998</v>
       </c>
-      <c r="D9">
-        <v>5.6503730000000001</v>
+      <c r="D9" s="6">
+        <f t="shared" si="0"/>
+        <v>9.4494571141436818</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>9.4494571141436818</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1.43801</v>
-      </c>
-      <c r="G9" s="5">
-        <v>7.2332419999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.40589199999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>64</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
         <v>4.221819</v>
       </c>
       <c r="C10">
         <v>0.44517200000000001</v>
       </c>
-      <c r="D10">
-        <v>5.6201809999999996</v>
+      <c r="D10" s="6">
+        <f t="shared" si="0"/>
+        <v>9.4835681489401846</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>9.4835681489401846</v>
-      </c>
-      <c r="F10" s="5">
-        <v>1.439022</v>
-      </c>
-      <c r="G10" s="5">
-        <v>6.5813569999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.40879700000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="15" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>2</v>
+      <c r="D15" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="6">
         <f>'Testing 1'!$B$40</f>
         <v>3.07422</v>
       </c>
       <c r="C16">
         <v>1.7803150000000001</v>
       </c>
-      <c r="D16">
-        <v>7.0986909999999996</v>
-      </c>
-      <c r="E16">
+      <c r="D16" s="6">
         <f>B16/C16</f>
         <v>1.7267843050246725</v>
       </c>
-      <c r="F16" s="5">
-        <v>1.540073</v>
-      </c>
-      <c r="G16" s="5">
-        <v>6.6633519999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>4</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="6">
         <f>'Testing 1'!$B$40</f>
         <v>3.07422</v>
       </c>
       <c r="C17">
         <v>0.91214399999999995</v>
       </c>
-      <c r="D17">
-        <v>5.3931120000000004</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ref="E17:E21" si="1">B17/C17</f>
+      <c r="D17" s="6">
+        <f t="shared" ref="D17:D21" si="1">B17/C17</f>
         <v>3.3703231068778616</v>
       </c>
-      <c r="F17" s="5">
-        <v>1.2319119999999999</v>
-      </c>
-      <c r="G17" s="5">
-        <v>6.6738819999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>8</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="6">
         <f>'Testing 1'!$B$40</f>
         <v>3.07422</v>
       </c>
       <c r="C18">
         <v>0.41222500000000001</v>
       </c>
-      <c r="D18">
-        <v>5.5883979999999998</v>
-      </c>
-      <c r="E18">
+      <c r="D18" s="6">
         <f t="shared" si="1"/>
         <v>7.4576262963187574</v>
       </c>
-      <c r="F18" s="5">
-        <v>1.4754229999999999</v>
-      </c>
-      <c r="G18" s="5">
-        <v>6.1407610000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="6">
         <f>'Testing 1'!$B$40</f>
         <v>3.07422</v>
       </c>
       <c r="C19">
         <v>0.248222</v>
       </c>
-      <c r="D19">
-        <v>5.4797409999999998</v>
-      </c>
-      <c r="E19">
+      <c r="D19" s="6">
         <f t="shared" si="1"/>
         <v>12.384961848667725</v>
       </c>
-      <c r="F19" s="5">
-        <v>1.988049</v>
-      </c>
-      <c r="G19" s="5">
-        <v>7.3005849999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>32</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="6">
         <f>'Testing 1'!$B$40</f>
         <v>3.07422</v>
       </c>
       <c r="C20">
         <v>0.18618000000000001</v>
       </c>
-      <c r="D20">
-        <v>4.9896700000000003</v>
-      </c>
-      <c r="E20">
+      <c r="D20" s="6">
         <f t="shared" si="1"/>
         <v>16.512085078955849</v>
       </c>
-      <c r="F20" s="5">
-        <v>1.7018230000000001</v>
-      </c>
-      <c r="G20" s="5">
-        <v>7.0630740000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>64</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="6">
         <f>'Testing 1'!$B$40</f>
         <v>3.07422</v>
       </c>
       <c r="C21">
         <v>0.175349</v>
       </c>
-      <c r="D21">
-        <v>4.7182089999999999</v>
-      </c>
-      <c r="E21">
+      <c r="D21" s="6">
         <f t="shared" si="1"/>
         <v>17.532007596279421</v>
       </c>
-      <c r="F21" s="5">
-        <v>1.561496</v>
-      </c>
-      <c r="G21" s="5">
-        <v>7.0868510000000002</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C14:E14"/>
+  <mergeCells count="2">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\graph\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9B89BC-13CF-408D-A557-8BCB70E161EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA12F6AD-4003-4515-B98B-C2EF19F9B491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -435,24 +435,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.6328125" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.6328125" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4"/>
       <c r="D1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -465,7 +465,7 @@
       </c>
       <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -485,7 +485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
@@ -507,7 +507,7 @@
         <v>10.71364513018322</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
@@ -529,7 +529,7 @@
         <v>10.667759142743463</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
@@ -551,7 +551,7 @@
         <v>10.84535826658329</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
@@ -573,7 +573,7 @@
         <v>10.77266482053467</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
@@ -595,7 +595,7 @@
         <v>10.550466388906163</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
@@ -617,7 +617,7 @@
         <v>10.513011318874913</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
@@ -639,7 +639,7 @@
         <v>10.801986269866958</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10.785536921360515</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
@@ -683,7 +683,7 @@
         <v>12.085767345233069</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
@@ -705,7 +705,7 @@
         <v>12.036656230496654</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
@@ -727,7 +727,7 @@
         <v>11.910308941962569</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
@@ -749,7 +749,7 @@
         <v>12.068078883784548</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
@@ -771,7 +771,7 @@
         <v>11.177408780875439</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
@@ -793,7 +793,7 @@
         <v>12.06552732331156</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
@@ -815,7 +815,7 @@
         <v>11.674188610802952</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
@@ -837,7 +837,7 @@
         <v>11.924051793782562</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
@@ -859,7 +859,7 @@
         <v>11.855845162666609</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
@@ -881,7 +881,7 @@
         <v>11.944374471155383</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
@@ -903,7 +903,7 @@
         <v>12.133607350009958</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
@@ -925,7 +925,7 @@
         <v>11.72925750072327</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
@@ -947,7 +947,7 @@
         <v>11.88343276981472</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
@@ -969,7 +969,7 @@
         <v>11.601988288024387</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
@@ -991,7 +991,7 @@
         <v>11.734277387055867</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>11.716702715761381</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>11.776534371558697</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>11.873285569720663</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>11.584143716551823</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>9.6451570703458867</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>9.8734344736249344</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>9.3583658664230285</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
@@ -1167,11 +1167,11 @@
         <v>9.2380823037587891</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B36"/>
       <c r="D36"/>
     </row>
-    <row r="37" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
         <v>3</v>
       </c>
@@ -1183,7 +1183,7 @@
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B38" s="5" t="s">
         <v>7</v>
       </c>
@@ -1197,7 +1197,7 @@
       <c r="F38" s="10"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -1217,686 +1217,686 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
       <c r="B40" s="6">
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C40">
         <v>0.19961499999999999</v>
       </c>
       <c r="D40" s="6">
         <f t="shared" ref="D40:D70" si="2">B40/C40</f>
-        <v>15.400746436891016</v>
+        <v>9.5660897227162298</v>
       </c>
       <c r="E40">
         <v>0.216973</v>
       </c>
       <c r="F40">
         <f>B40/E40</f>
-        <v>14.168675365137597</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8.8007954906831731</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
       <c r="B41" s="6">
-        <v>4.0935550000000003</v>
+        <v>2.0607150000000001</v>
       </c>
       <c r="C41">
         <v>0.208622</v>
       </c>
       <c r="D41" s="6">
         <f t="shared" si="2"/>
-        <v>19.621875928713177</v>
+        <v>9.877745395979332</v>
       </c>
       <c r="E41">
         <v>0.21165</v>
       </c>
       <c r="F41">
         <f t="shared" ref="F41:F70" si="3">B41/E41</f>
-        <v>19.341152846680842</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9.7364280652019843</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
       <c r="B42" s="6">
-        <v>4.904312</v>
+        <v>2.3441619999999999</v>
       </c>
       <c r="C42">
         <v>0.230629</v>
       </c>
       <c r="D42" s="6">
         <f t="shared" si="2"/>
-        <v>21.264940662275777</v>
+        <v>10.164211786028643</v>
       </c>
       <c r="E42">
         <v>0.245451</v>
       </c>
       <c r="F42">
         <f t="shared" si="3"/>
-        <v>19.980818982200113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>9.5504275802502328</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
       <c r="B43" s="6">
-        <v>5.4954840000000003</v>
+        <v>2.618735</v>
       </c>
       <c r="C43">
         <v>0.268316</v>
       </c>
       <c r="D43" s="6">
         <f t="shared" si="2"/>
-        <v>20.481387617585238</v>
+        <v>9.7598913221723649</v>
       </c>
       <c r="E43">
         <v>0.25640299999999999</v>
       </c>
       <c r="F43">
         <f t="shared" si="3"/>
-        <v>21.432994153734551</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.213355537961725</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
       <c r="B44" s="6">
-        <v>6.1328820000000004</v>
+        <v>2.932696</v>
       </c>
       <c r="C44">
         <v>0.29424</v>
       </c>
       <c r="D44" s="6">
         <f t="shared" si="2"/>
-        <v>20.843128058727572</v>
+        <v>9.9670201196302344</v>
       </c>
       <c r="E44">
         <v>0.28809899999999999</v>
       </c>
       <c r="F44">
         <f t="shared" si="3"/>
-        <v>21.287411618922665</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.17947302836872</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
       <c r="B45" s="6">
-        <v>6.7988749999999998</v>
+        <v>2.935181</v>
       </c>
       <c r="C45">
         <v>0.319859</v>
       </c>
       <c r="D45" s="6">
         <f t="shared" si="2"/>
-        <v>21.255850234009358</v>
+        <v>9.1764840132683467</v>
       </c>
       <c r="E45">
         <v>0.329737</v>
       </c>
       <c r="F45">
         <f t="shared" si="3"/>
-        <v>20.619084300518292</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8.90158217003248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
       <c r="B46" s="6">
-        <v>7.4492789999999998</v>
+        <v>2.9385319999999999</v>
       </c>
       <c r="C46">
         <v>0.374307</v>
       </c>
       <c r="D46" s="6">
         <f t="shared" si="2"/>
-        <v>19.901522012679433</v>
+        <v>7.8505932296216736</v>
       </c>
       <c r="E46">
         <v>0.34054099999999998</v>
       </c>
       <c r="F46">
         <f t="shared" si="3"/>
-        <v>21.874837391092409</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8.6290108973662498</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
       <c r="B47" s="6">
-        <v>7.9789300000000001</v>
+        <v>3.1479159999999999</v>
       </c>
       <c r="C47">
         <v>0.41203099999999998</v>
       </c>
       <c r="D47" s="6">
         <f t="shared" si="2"/>
-        <v>19.364877885401828</v>
+        <v>7.6399979613184446</v>
       </c>
       <c r="E47">
         <v>0.37627100000000002</v>
       </c>
       <c r="F47">
         <f t="shared" si="3"/>
-        <v>21.205274921532617</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+        <v>8.3660872084215896</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
       <c r="B48" s="6">
-        <v>8.7212800000000001</v>
+        <v>3.984353</v>
       </c>
       <c r="C48">
         <v>0.39272200000000002</v>
       </c>
       <c r="D48" s="6">
         <f t="shared" si="2"/>
-        <v>22.207261116005725</v>
+        <v>10.14547949949328</v>
       </c>
       <c r="E48">
         <v>0.39349200000000001</v>
       </c>
       <c r="F48">
         <f t="shared" si="3"/>
-        <v>22.163805109125473</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10.125626442214836</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
       <c r="B49" s="6">
-        <v>9.3753119999999992</v>
+        <v>4.5080559999999998</v>
       </c>
       <c r="C49">
         <v>0.41116200000000003</v>
       </c>
       <c r="D49" s="6">
         <f t="shared" si="2"/>
-        <v>22.801990456316485</v>
+        <v>10.964184433386352</v>
       </c>
       <c r="E49">
         <v>0.42541000000000001</v>
       </c>
       <c r="F49">
         <f t="shared" si="3"/>
-        <v>22.038297172139817</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10.596967631226345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
       <c r="B50" s="6">
-        <v>10.080152999999999</v>
+        <v>4.8301439999999998</v>
       </c>
       <c r="C50">
         <v>0.46141599999999999</v>
       </c>
       <c r="D50" s="6">
         <f t="shared" si="2"/>
-        <v>21.846128005964246</v>
+        <v>10.468089533089445</v>
       </c>
       <c r="E50">
         <v>0.44863900000000001</v>
       </c>
       <c r="F50">
         <f t="shared" si="3"/>
-        <v>22.46829410728893</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10.766215152940337</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
       <c r="B51" s="6">
-        <v>10.752592999999999</v>
+        <v>4.261908</v>
       </c>
       <c r="C51">
         <v>0.64751300000000001</v>
       </c>
       <c r="D51" s="6">
         <f t="shared" si="2"/>
-        <v>16.605987833448904</v>
+        <v>6.5819651497344456</v>
       </c>
       <c r="E51">
         <v>0.459978</v>
       </c>
       <c r="F51">
         <f t="shared" si="3"/>
-        <v>23.376320171834305</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.2654605220249664</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
       <c r="B52" s="6">
-        <v>11.561036</v>
+        <v>4.6739220000000001</v>
       </c>
       <c r="C52">
         <v>0.73573200000000005</v>
       </c>
       <c r="D52" s="6">
         <f t="shared" si="2"/>
-        <v>15.71365116645735</v>
+        <v>6.3527507298853383</v>
       </c>
       <c r="E52">
         <v>0.50284499999999999</v>
       </c>
       <c r="F52">
         <f t="shared" si="3"/>
-        <v>22.991251777386669</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.2949557020553062</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
       <c r="B53" s="6">
-        <v>12.216346</v>
+        <v>5.8025909999999996</v>
       </c>
       <c r="C53">
         <v>0.65195899999999996</v>
       </c>
       <c r="D53" s="6">
         <f t="shared" si="2"/>
-        <v>18.737905297725778</v>
+        <v>8.900239125466479</v>
       </c>
       <c r="E53">
         <v>0.53020299999999998</v>
       </c>
       <c r="F53">
         <f t="shared" si="3"/>
-        <v>23.040884340526176</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10.944093111506348</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
       <c r="B54" s="6">
-        <v>13.036834000000001</v>
+        <v>6.2275739999999997</v>
       </c>
       <c r="C54">
         <v>0.62831400000000004</v>
       </c>
       <c r="D54" s="6">
         <f t="shared" si="2"/>
-        <v>20.748915351241575</v>
+        <v>9.9115633266169461</v>
       </c>
       <c r="E54">
         <v>0.55043200000000003</v>
       </c>
       <c r="F54">
         <f t="shared" si="3"/>
-        <v>23.684731265624091</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11.313975204929944</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
       <c r="B55" s="6">
-        <v>13.817802</v>
+        <v>5.5089629999999996</v>
       </c>
       <c r="C55">
         <v>0.62590500000000004</v>
       </c>
       <c r="D55" s="6">
         <f t="shared" si="2"/>
-        <v>22.07651640424665</v>
+        <v>8.8015960888633238</v>
       </c>
       <c r="E55">
         <v>0.60006199999999998</v>
       </c>
       <c r="F55">
         <f t="shared" si="3"/>
-        <v>23.027290513313627</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.1806563321790069</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
       <c r="B56" s="6">
-        <v>14.610976000000001</v>
+        <v>6.759309</v>
       </c>
       <c r="C56">
         <v>0.64108600000000004</v>
       </c>
       <c r="D56" s="6">
         <f t="shared" si="2"/>
-        <v>22.790976561646954</v>
+        <v>10.543529261284757</v>
       </c>
       <c r="E56">
         <v>0.68986199999999998</v>
       </c>
       <c r="F56">
         <f t="shared" si="3"/>
-        <v>21.17956344892167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.7980596119223851</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
       <c r="B57" s="6">
-        <v>15.201309999999999</v>
+        <v>7.3081040000000002</v>
       </c>
       <c r="C57">
         <v>0.68704200000000004</v>
       </c>
       <c r="D57" s="6">
         <f t="shared" si="2"/>
-        <v>22.125736126757896</v>
+        <v>10.637055667630218</v>
       </c>
       <c r="E57">
         <v>0.64302199999999998</v>
       </c>
       <c r="F57">
         <f t="shared" si="3"/>
-        <v>23.640419767908408</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11.365247223267634</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
       <c r="B58" s="6">
-        <v>16.062538</v>
+        <v>7.7859230000000004</v>
       </c>
       <c r="C58">
         <v>0.85647399999999996</v>
       </c>
       <c r="D58" s="6">
         <f t="shared" si="2"/>
-        <v>18.754262242636671</v>
+        <v>9.0906705866144222</v>
       </c>
       <c r="E58">
         <v>0.71674599999999999</v>
       </c>
       <c r="F58">
         <f t="shared" si="3"/>
-        <v>22.410362945869249</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10.862876109528342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
       <c r="B59" s="6">
-        <v>16.927885</v>
+        <v>8.1711229999999997</v>
       </c>
       <c r="C59">
         <v>0.87755899999999998</v>
       </c>
       <c r="D59" s="6">
         <f t="shared" si="2"/>
-        <v>19.289740063061288</v>
+        <v>9.3111950307614642</v>
       </c>
       <c r="E59">
         <v>0.73519000000000001</v>
       </c>
       <c r="F59">
         <f t="shared" si="3"/>
-        <v>23.025183966049592</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+        <v>11.114301065030809</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
       <c r="B60" s="6">
-        <v>17.821466000000001</v>
+        <v>7.8258559999999999</v>
       </c>
       <c r="C60">
         <v>0.91805499999999995</v>
       </c>
       <c r="D60" s="6">
         <f t="shared" si="2"/>
-        <v>19.412198615551358</v>
+        <v>8.5243868831388099</v>
       </c>
       <c r="E60">
         <v>0.89686399999999999</v>
       </c>
       <c r="F60">
         <f t="shared" si="3"/>
-        <v>19.870867823884112</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8.7258001213115932</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
       <c r="B61" s="6">
-        <v>18.579981</v>
+        <v>8.2571309999999993</v>
       </c>
       <c r="C61">
         <v>0.94625599999999999</v>
       </c>
       <c r="D61" s="6">
         <f t="shared" si="2"/>
-        <v>19.635258323328994</v>
+        <v>8.7261068886221054</v>
       </c>
       <c r="E61">
         <v>0.85248999999999997</v>
       </c>
       <c r="F61">
         <f t="shared" si="3"/>
-        <v>21.794954779528208</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.6858977817921605</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
       <c r="B62" s="6">
-        <v>19.452786</v>
+        <v>9.3257549999999991</v>
       </c>
       <c r="C62">
         <v>0.89138200000000001</v>
       </c>
       <c r="D62" s="6">
         <f t="shared" si="2"/>
-        <v>21.823175697961144</v>
+        <v>10.462130713880244</v>
       </c>
       <c r="E62">
         <v>0.96400200000000003</v>
       </c>
       <c r="F62">
         <f t="shared" si="3"/>
-        <v>20.179196723658247</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.6739996390048972</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
       <c r="B63" s="6">
-        <v>20.361827999999999</v>
+        <v>9.1804319999999997</v>
       </c>
       <c r="C63">
         <v>1.0145040000000001</v>
       </c>
       <c r="D63" s="6">
         <f t="shared" si="2"/>
-        <v>20.070722244564831</v>
+        <v>9.0491826547751408</v>
       </c>
       <c r="E63">
         <v>0.87285800000000002</v>
       </c>
       <c r="F63">
         <f t="shared" si="3"/>
-        <v>23.327766944909708</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+        <v>10.517669540750042</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
       <c r="B64" s="6">
-        <v>21.225096000000001</v>
+        <v>7.4094749999999996</v>
       </c>
       <c r="C64">
         <v>1.081969</v>
       </c>
       <c r="D64" s="6">
         <f t="shared" si="2"/>
-        <v>19.617101783877359</v>
+        <v>6.8481398265569533</v>
       </c>
       <c r="E64">
         <v>0.89015500000000003</v>
       </c>
       <c r="F64">
         <f t="shared" si="3"/>
-        <v>23.844269818177732</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8.3238031578769984</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
       <c r="B65" s="6">
-        <v>22.179998999999999</v>
+        <v>8.2858409999999996</v>
       </c>
       <c r="C65">
         <v>1.1624030000000001</v>
       </c>
       <c r="D65" s="6">
         <f t="shared" si="2"/>
-        <v>19.081161180760887</v>
+        <v>7.1281999444254698</v>
       </c>
       <c r="E65">
         <v>0.985043</v>
       </c>
       <c r="F65">
         <f t="shared" si="3"/>
-        <v>22.516782516093205</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8.4116541105312148</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
       <c r="B66" s="6">
-        <v>23.211036</v>
+        <v>10.00493</v>
       </c>
       <c r="C66">
         <v>1.1323209999999999</v>
       </c>
       <c r="D66" s="6">
         <f t="shared" si="2"/>
-        <v>20.498635987498247</v>
+        <v>8.8357718350185159</v>
       </c>
       <c r="E66">
         <v>1.027749</v>
       </c>
       <c r="F66">
         <f t="shared" si="3"/>
-        <v>22.584343064308502</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.7347990608601904</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
       <c r="B67" s="6">
-        <v>23.925511</v>
+        <v>9.4460809999999995</v>
       </c>
       <c r="C67">
         <v>1.200993</v>
       </c>
       <c r="D67" s="6">
         <f t="shared" si="2"/>
-        <v>19.921440841037377</v>
+        <v>7.8652256924062005</v>
       </c>
       <c r="E67">
         <v>1.011207</v>
       </c>
       <c r="F67">
         <f t="shared" si="3"/>
-        <v>23.660349463561865</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.3413920196359399</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
       <c r="B68" s="6">
-        <v>24.83474</v>
+        <v>11.223677</v>
       </c>
       <c r="C68">
         <v>1.212243</v>
       </c>
       <c r="D68" s="6">
         <f t="shared" si="2"/>
-        <v>20.486602108653134</v>
+        <v>9.258603266836765</v>
       </c>
       <c r="E68">
         <v>1.143842</v>
       </c>
       <c r="F68">
         <f t="shared" si="3"/>
-        <v>21.711687453337085</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>9.8122616585157747</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
       <c r="B69" s="6">
-        <v>25.810836999999999</v>
+        <v>9.0509140000000006</v>
       </c>
       <c r="C69">
         <v>1.2506710000000001</v>
       </c>
       <c r="D69" s="6">
         <f t="shared" si="2"/>
-        <v>20.637591340968168</v>
+        <v>7.236846460819832</v>
       </c>
       <c r="E69">
         <v>1.156982</v>
       </c>
       <c r="F69">
         <f t="shared" si="3"/>
-        <v>22.308762798384073</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7.822865005678568</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>40000000</v>
       </c>
       <c r="B70" s="6">
-        <v>26.719480000000001</v>
+        <v>11.736215</v>
       </c>
       <c r="C70">
         <v>1.263007</v>
       </c>
       <c r="D70" s="6">
         <f t="shared" si="2"/>
-        <v>21.155448861328562</v>
+        <v>9.2922802486447029</v>
       </c>
       <c r="E70">
         <v>1.105423</v>
       </c>
       <c r="F70">
         <f t="shared" si="3"/>
-        <v>24.171271992712292</v>
+        <v>10.616944825645929</v>
       </c>
     </row>
   </sheetData>
@@ -1914,19 +1914,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="22.6328125" customWidth="1"/>
-    <col min="5" max="5" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>2.0506150000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>0.62085500000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>0.39751399999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>16</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>0.39396199999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>32</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>0.40589199999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64</v>
       </c>
@@ -2063,17 +2063,17 @@
         <v>0.40879700000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -2102,100 +2102,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16" s="6">
         <f>'Testing 1'!$B$40</f>
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C16">
         <v>1.7803150000000001</v>
       </c>
       <c r="D16" s="6">
         <f>B16/C16</f>
-        <v>1.7267843050246725</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+        <v>1.0725826609335987</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
       <c r="B17" s="6">
         <f>'Testing 1'!$B$40</f>
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C17">
         <v>0.91214399999999995</v>
       </c>
       <c r="D17" s="6">
         <f t="shared" ref="D17:D21" si="1">B17/C17</f>
-        <v>3.3703231068778616</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>2.0934578312196321</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>8</v>
       </c>
       <c r="B18" s="6">
         <f>'Testing 1'!$B$40</f>
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C18">
         <v>0.41222500000000001</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="1"/>
-        <v>7.4576262963187574</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+        <v>4.6322639335314451</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" s="6">
         <f>'Testing 1'!$B$40</f>
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C19">
         <v>0.248222</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="1"/>
-        <v>12.384961848667725</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+        <v>7.6928515602968313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
       <c r="B20" s="6">
         <f>'Testing 1'!$B$40</f>
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C20">
         <v>0.18618000000000001</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="1"/>
-        <v>16.512085078955849</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+        <v>10.256391663981093</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>64</v>
       </c>
       <c r="B21" s="6">
         <f>'Testing 1'!$B$40</f>
-        <v>3.07422</v>
+        <v>1.909535</v>
       </c>
       <c r="C21">
         <v>0.175349</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" si="1"/>
-        <v>17.532007596279421</v>
+        <v>10.889910977536227</v>
       </c>
     </row>
   </sheetData>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA12F6AD-4003-4515-B98B-C2EF19F9B491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE537F0C-7CAD-4D62-BDC9-55BD20E3D53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -1232,11 +1232,11 @@
         <v>9.5660897227162298</v>
       </c>
       <c r="E40">
-        <v>0.216973</v>
+        <v>0.17649999999999999</v>
       </c>
       <c r="F40">
         <f>B40/E40</f>
-        <v>8.8007954906831731</v>
+        <v>10.818895184135977</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -1254,11 +1254,11 @@
         <v>9.877745395979332</v>
       </c>
       <c r="E41">
-        <v>0.21165</v>
+        <v>0.14477699999999999</v>
       </c>
       <c r="F41">
         <f t="shared" ref="F41:F70" si="3">B41/E41</f>
-        <v>9.7364280652019843</v>
+        <v>14.23371806295199</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -1276,11 +1276,11 @@
         <v>10.164211786028643</v>
       </c>
       <c r="E42">
-        <v>0.245451</v>
+        <v>0.140874</v>
       </c>
       <c r="F42">
         <f t="shared" si="3"/>
-        <v>9.5504275802502328</v>
+        <v>16.640132316822125</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -1298,11 +1298,11 @@
         <v>9.7598913221723649</v>
       </c>
       <c r="E43">
-        <v>0.25640299999999999</v>
+        <v>0.15146899999999999</v>
       </c>
       <c r="F43">
         <f t="shared" si="3"/>
-        <v>10.213355537961725</v>
+        <v>17.288917204180393</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
@@ -1320,11 +1320,11 @@
         <v>9.9670201196302344</v>
       </c>
       <c r="E44">
-        <v>0.28809899999999999</v>
+        <v>0.166132</v>
       </c>
       <c r="F44">
         <f t="shared" si="3"/>
-        <v>10.17947302836872</v>
+        <v>17.652806202296969</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -1342,11 +1342,11 @@
         <v>9.1764840132683467</v>
       </c>
       <c r="E45">
-        <v>0.329737</v>
+        <v>0.183388</v>
       </c>
       <c r="F45">
         <f t="shared" si="3"/>
-        <v>8.90158217003248</v>
+        <v>16.005305690666784</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -1364,11 +1364,11 @@
         <v>7.8505932296216736</v>
       </c>
       <c r="E46">
-        <v>0.34054099999999998</v>
+        <v>0.199738</v>
       </c>
       <c r="F46">
         <f t="shared" si="3"/>
-        <v>8.6290108973662498</v>
+        <v>14.711932631747588</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -1386,11 +1386,11 @@
         <v>7.6399979613184446</v>
       </c>
       <c r="E47">
-        <v>0.37627100000000002</v>
+        <v>0.22170100000000001</v>
       </c>
       <c r="F47">
         <f t="shared" si="3"/>
-        <v>8.3660872084215896</v>
+        <v>14.198925579947767</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -1408,11 +1408,11 @@
         <v>10.14547949949328</v>
       </c>
       <c r="E48">
-        <v>0.39349200000000001</v>
+        <v>0.23760600000000001</v>
       </c>
       <c r="F48">
         <f t="shared" si="3"/>
-        <v>10.125626442214836</v>
+        <v>16.768739004907282</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1430,11 +1430,11 @@
         <v>10.964184433386352</v>
       </c>
       <c r="E49">
-        <v>0.42541000000000001</v>
+        <v>0.25980799999999998</v>
       </c>
       <c r="F49">
         <f t="shared" si="3"/>
-        <v>10.596967631226345</v>
+        <v>17.351490331321592</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1452,11 +1452,11 @@
         <v>10.468089533089445</v>
       </c>
       <c r="E50">
-        <v>0.44863900000000001</v>
+        <v>0.27559299999999998</v>
       </c>
       <c r="F50">
         <f t="shared" si="3"/>
-        <v>10.766215152940337</v>
+        <v>17.526366779998042</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1474,11 +1474,11 @@
         <v>6.5819651497344456</v>
       </c>
       <c r="E51">
-        <v>0.459978</v>
+        <v>0.303315</v>
       </c>
       <c r="F51">
         <f t="shared" si="3"/>
-        <v>9.2654605220249664</v>
+        <v>14.051095395875574</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -1496,11 +1496,11 @@
         <v>6.3527507298853383</v>
       </c>
       <c r="E52">
-        <v>0.50284499999999999</v>
+        <v>0.344914</v>
       </c>
       <c r="F52">
         <f t="shared" si="3"/>
-        <v>9.2949557020553062</v>
+        <v>13.550977924932013</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -1518,11 +1518,11 @@
         <v>8.900239125466479</v>
       </c>
       <c r="E53">
-        <v>0.53020299999999998</v>
+        <v>0.33877099999999999</v>
       </c>
       <c r="F53">
         <f t="shared" si="3"/>
-        <v>10.944093111506348</v>
+        <v>17.128358094405954</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1540,11 +1540,11 @@
         <v>9.9115633266169461</v>
       </c>
       <c r="E54">
-        <v>0.55043200000000003</v>
+        <v>0.36179899999999998</v>
       </c>
       <c r="F54">
         <f t="shared" si="3"/>
-        <v>11.313975204929944</v>
+        <v>17.212800477613261</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -1562,11 +1562,11 @@
         <v>8.8015960888633238</v>
       </c>
       <c r="E55">
-        <v>0.60006199999999998</v>
+        <v>0.37873499999999999</v>
       </c>
       <c r="F55">
         <f t="shared" si="3"/>
-        <v>9.1806563321790069</v>
+        <v>14.545692898728662</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -1584,11 +1584,11 @@
         <v>10.543529261284757</v>
       </c>
       <c r="E56">
-        <v>0.68986199999999998</v>
+        <v>0.402088</v>
       </c>
       <c r="F56">
         <f t="shared" si="3"/>
-        <v>9.7980596119223851</v>
+        <v>16.810521577366149</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -1606,11 +1606,11 @@
         <v>10.637055667630218</v>
       </c>
       <c r="E57">
-        <v>0.64302199999999998</v>
+        <v>0.42627999999999999</v>
       </c>
       <c r="F57">
         <f t="shared" si="3"/>
-        <v>11.365247223267634</v>
+        <v>17.143905414281694</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -1628,11 +1628,11 @@
         <v>9.0906705866144222</v>
       </c>
       <c r="E58">
-        <v>0.71674599999999999</v>
+        <v>0.46981200000000001</v>
       </c>
       <c r="F58">
         <f t="shared" si="3"/>
-        <v>10.862876109528342</v>
+        <v>16.572422586055698</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -1650,11 +1650,11 @@
         <v>9.3111950307614642</v>
       </c>
       <c r="E59">
-        <v>0.73519000000000001</v>
+        <v>0.48134700000000002</v>
       </c>
       <c r="F59">
         <f t="shared" si="3"/>
-        <v>11.114301065030809</v>
+        <v>16.975535320673025</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -1672,11 +1672,11 @@
         <v>8.5243868831388099</v>
       </c>
       <c r="E60">
-        <v>0.89686399999999999</v>
+        <v>0.49238599999999999</v>
       </c>
       <c r="F60">
         <f t="shared" si="3"/>
-        <v>8.7258001213115932</v>
+        <v>15.893741901678764</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -1694,11 +1694,11 @@
         <v>8.7261068886221054</v>
       </c>
       <c r="E61">
-        <v>0.85248999999999997</v>
+        <v>0.51916799999999996</v>
       </c>
       <c r="F61">
         <f t="shared" si="3"/>
-        <v>9.6858977817921605</v>
+        <v>15.904545349482248</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -1716,11 +1716,11 @@
         <v>10.462130713880244</v>
       </c>
       <c r="E62">
-        <v>0.96400200000000003</v>
+        <v>0.54023399999999999</v>
       </c>
       <c r="F62">
         <f t="shared" si="3"/>
-        <v>9.6739996390048972</v>
+        <v>17.262436277613034</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -1738,11 +1738,11 @@
         <v>9.0491826547751408</v>
       </c>
       <c r="E63">
-        <v>0.87285800000000002</v>
+        <v>0.56404299999999996</v>
       </c>
       <c r="F63">
         <f t="shared" si="3"/>
-        <v>10.517669540750042</v>
+        <v>16.276120792209106</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -1760,11 +1760,11 @@
         <v>6.8481398265569533</v>
       </c>
       <c r="E64">
-        <v>0.89015500000000003</v>
+        <v>0.80766700000000002</v>
       </c>
       <c r="F64">
         <f t="shared" si="3"/>
-        <v>8.3238031578769984</v>
+        <v>9.1739231638781824</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -1782,11 +1782,11 @@
         <v>7.1281999444254698</v>
       </c>
       <c r="E65">
-        <v>0.985043</v>
+        <v>1.033277</v>
       </c>
       <c r="F65">
         <f t="shared" si="3"/>
-        <v>8.4116541105312148</v>
+        <v>8.0189929709071226</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -1804,11 +1804,11 @@
         <v>8.8357718350185159</v>
       </c>
       <c r="E66">
-        <v>1.027749</v>
+        <v>1.081855</v>
       </c>
       <c r="F66">
         <f t="shared" si="3"/>
-        <v>9.7347990608601904</v>
+        <v>9.2479398810376612</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -1826,11 +1826,11 @@
         <v>7.8652256924062005</v>
       </c>
       <c r="E67">
-        <v>1.011207</v>
+        <v>0.92883599999999999</v>
       </c>
       <c r="F67">
         <f t="shared" si="3"/>
-        <v>9.3413920196359399</v>
+        <v>10.169805003251382</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -1848,11 +1848,11 @@
         <v>9.258603266836765</v>
       </c>
       <c r="E68">
-        <v>1.143842</v>
+        <v>0.69468200000000002</v>
       </c>
       <c r="F68">
         <f t="shared" si="3"/>
-        <v>9.8122616585157747</v>
+        <v>16.156568041204466</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -1870,11 +1870,11 @@
         <v>7.236846460819832</v>
       </c>
       <c r="E69">
-        <v>1.156982</v>
+        <v>0.72290900000000002</v>
       </c>
       <c r="F69">
         <f t="shared" si="3"/>
-        <v>7.822865005678568</v>
+        <v>12.520129089553457</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -1892,11 +1892,11 @@
         <v>9.2922802486447029</v>
       </c>
       <c r="E70">
-        <v>1.105423</v>
+        <v>0.74537900000000001</v>
       </c>
       <c r="F70">
         <f t="shared" si="3"/>
-        <v>10.616944825645929</v>
+        <v>15.745298700392686</v>
       </c>
     </row>
   </sheetData>
@@ -2107,95 +2107,107 @@
         <v>1</v>
       </c>
       <c r="B16" s="6">
-        <f>'Testing 1'!$B$40</f>
-        <v>1.909535</v>
+        <v>1.819431</v>
       </c>
       <c r="C16">
         <v>1.7803150000000001</v>
       </c>
       <c r="D16" s="6">
         <f>B16/C16</f>
-        <v>1.0725826609335987</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.0219713927029768</v>
+      </c>
+      <c r="E16">
+        <v>1.794886</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
       <c r="B17" s="6">
-        <f>'Testing 1'!$B$40</f>
-        <v>1.909535</v>
+        <v>1.819431</v>
       </c>
       <c r="C17">
         <v>0.91214399999999995</v>
       </c>
       <c r="D17" s="6">
         <f t="shared" ref="D17:D21" si="1">B17/C17</f>
-        <v>2.0934578312196321</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1.9946751828658633</v>
+      </c>
+      <c r="E17">
+        <v>0.43836999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>8</v>
       </c>
       <c r="B18" s="6">
-        <f>'Testing 1'!$B$40</f>
-        <v>1.909535</v>
+        <v>1.819431</v>
       </c>
       <c r="C18">
         <v>0.41222500000000001</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="1"/>
-        <v>4.6322639335314451</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4.4136842743647282</v>
+      </c>
+      <c r="E18">
+        <v>0.225991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
       <c r="B19" s="6">
-        <f>'Testing 1'!$B$40</f>
-        <v>1.909535</v>
+        <v>1.819431</v>
       </c>
       <c r="C19">
         <v>0.248222</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="1"/>
-        <v>7.6928515602968313</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7.3298539210867695</v>
+      </c>
+      <c r="E19">
+        <v>0.15532199999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
       <c r="B20" s="6">
-        <f>'Testing 1'!$B$40</f>
-        <v>1.909535</v>
+        <v>1.819431</v>
       </c>
       <c r="C20">
         <v>0.18618000000000001</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="1"/>
-        <v>10.256391663981093</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>9.7724299065420563</v>
+      </c>
+      <c r="E20">
+        <v>0.14178299999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>64</v>
       </c>
       <c r="B21" s="6">
-        <f>'Testing 1'!$B$40</f>
-        <v>1.909535</v>
+        <v>1.819431</v>
       </c>
       <c r="C21">
         <v>0.175349</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" si="1"/>
-        <v>10.889910977536227</v>
+        <v>10.376055751672379</v>
+      </c>
+      <c r="E21">
+        <v>0.141709</v>
       </c>
     </row>
   </sheetData>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\graph\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE537F0C-7CAD-4D62-BDC9-55BD20E3D53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C4B56E-1352-40AA-98A0-2B0DE9B68D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -142,17 +142,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,37 +435,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="22.6328125" customWidth="1"/>
+    <col min="2" max="2" width="22.6328125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22.6328125" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4"/>
       <c r="D1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -485,719 +485,719 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
       <c r="B5" s="6">
-        <v>4.221819</v>
+        <v>1.981976</v>
       </c>
       <c r="C5">
         <v>0.66401900000000003</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5:D35" si="0">B5/C5</f>
-        <v>6.3579792144501885</v>
+        <v>2.9848182055031556</v>
       </c>
       <c r="E5">
         <v>0.39406000000000002</v>
       </c>
       <c r="F5">
         <f>B5/E5</f>
-        <v>10.71364513018322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0296300055829057</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
       <c r="B6" s="6">
-        <v>4.7456699999999996</v>
+        <v>2.2297829999999998</v>
       </c>
       <c r="C6">
         <v>0.76085100000000006</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="0"/>
-        <v>6.2373184762851057</v>
+        <v>2.9306434505573362</v>
       </c>
       <c r="E6">
         <v>0.44486100000000001</v>
       </c>
       <c r="F6">
         <f t="shared" ref="F6:F35" si="1">B6/E6</f>
-        <v>10.667759142743463</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0123139587421681</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
       <c r="B7" s="6">
-        <v>5.4632949999999996</v>
+        <v>2.5267469999999999</v>
       </c>
       <c r="C7">
         <v>0.84793499999999999</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="0"/>
-        <v>6.4430587250201956</v>
+        <v>2.9798828919669549</v>
       </c>
       <c r="E7">
         <v>0.503745</v>
       </c>
       <c r="F7">
         <f t="shared" si="1"/>
-        <v>10.84535826658329</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.015924723818598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
       <c r="B8" s="6">
-        <v>6.0686730000000004</v>
+        <v>2.9097770000000001</v>
       </c>
       <c r="C8">
         <v>0.93635000000000002</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="0"/>
-        <v>6.4812014738078716</v>
+        <v>3.1075740908848188</v>
       </c>
       <c r="E8">
         <v>0.56333999999999995</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>10.77266482053467</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.1652234884794268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
       <c r="B9" s="6">
-        <v>6.7864820000000003</v>
+        <v>3.1935090000000002</v>
       </c>
       <c r="C9">
         <v>1.0725750000000001</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="0"/>
-        <v>6.3272796774118358</v>
+        <v>2.9774225578630866</v>
       </c>
       <c r="E9">
         <v>0.64324000000000003</v>
       </c>
       <c r="F9">
         <f t="shared" si="1"/>
-        <v>10.550466388906163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9647238977675521</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
       <c r="B10" s="6">
-        <v>7.5130920000000003</v>
+        <v>3.5089090000000001</v>
       </c>
       <c r="C10">
         <v>1.16066</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v>6.4731204659417916</v>
+        <v>3.0232014543449415</v>
       </c>
       <c r="E10">
         <v>0.71464700000000003</v>
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>10.513011318874913</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.909989127499311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
       <c r="B11" s="6">
-        <v>8.2434170000000009</v>
+        <v>3.8552059999999999</v>
       </c>
       <c r="C11">
         <v>1.268275</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="0"/>
-        <v>6.4997078709270468</v>
+        <v>3.0397240346139438</v>
       </c>
       <c r="E11">
         <v>0.76313900000000001</v>
       </c>
       <c r="F11">
         <f t="shared" si="1"/>
-        <v>10.801986269866958</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0517743163434181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
       <c r="B12" s="6">
-        <v>9.0389809999999997</v>
+        <v>4.1694719999999998</v>
       </c>
       <c r="C12">
         <v>1.3796630000000001</v>
       </c>
       <c r="D12" s="6">
         <f t="shared" si="0"/>
-        <v>6.5515861482115554</v>
+        <v>3.0220945259820691</v>
       </c>
       <c r="E12">
         <v>0.83806499999999995</v>
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>10.785536921360515</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9751176818027245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
       <c r="B13" s="6">
-        <v>11.076497</v>
+        <v>4.5304719999999996</v>
       </c>
       <c r="C13">
         <v>1.566074</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="0"/>
-        <v>7.0727800857430747</v>
+        <v>2.8928850105422859</v>
       </c>
       <c r="E13">
         <v>0.91649099999999994</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>12.085767345233069</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9432804031899931</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
       <c r="B14" s="6">
-        <v>11.668153999999999</v>
+        <v>4.9316899999999997</v>
       </c>
       <c r="C14">
         <v>1.6360399999999999</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="0"/>
-        <v>7.1319490965991053</v>
+        <v>3.0144067382215591</v>
       </c>
       <c r="E14">
         <v>0.96938500000000005</v>
       </c>
       <c r="F14">
         <f t="shared" si="1"/>
-        <v>12.036656230496654</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.08744203799316</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
       <c r="B15" s="6">
-        <v>12.374013</v>
+        <v>5.2636799999999999</v>
       </c>
       <c r="C15">
         <v>1.75071</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="0"/>
-        <v>7.0679969840807439</v>
+        <v>3.0065973233716607</v>
       </c>
       <c r="E15">
         <v>1.0389330000000001</v>
       </c>
       <c r="F15">
         <f t="shared" si="1"/>
-        <v>11.910308941962569</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0664287302453568</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
       <c r="B16" s="6">
-        <v>13.410712999999999</v>
+        <v>5.5957280000000003</v>
       </c>
       <c r="C16">
         <v>1.9254990000000001</v>
       </c>
       <c r="D16" s="6">
         <f t="shared" si="0"/>
-        <v>6.9647987352888778</v>
+        <v>2.9061183620453712</v>
       </c>
       <c r="E16">
         <v>1.1112550000000001</v>
       </c>
       <c r="F16">
         <f t="shared" si="1"/>
-        <v>12.068078883784548</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0355031023482457</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
       <c r="B17" s="6">
-        <v>13.503204</v>
+        <v>6.0139670000000001</v>
       </c>
       <c r="C17">
         <v>2.0128330000000001</v>
       </c>
       <c r="D17" s="6">
         <f t="shared" si="0"/>
-        <v>6.708556546916709</v>
+        <v>2.987812202999454</v>
       </c>
       <c r="E17">
         <v>1.20808</v>
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>11.177408780875439</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9781198265015565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
       <c r="B18" s="6">
-        <v>15.334875</v>
+        <v>6.3563710000000002</v>
       </c>
       <c r="C18">
         <v>2.1030869999999999</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="0"/>
-        <v>7.2916027724958603</v>
+        <v>3.0224004047383684</v>
       </c>
       <c r="E18">
         <v>1.270966</v>
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>12.06552732331156</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0012124635906865</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
       <c r="B19" s="6">
-        <v>15.795399</v>
+        <v>6.8612270000000004</v>
       </c>
       <c r="C19">
         <v>2.2671899999999998</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="0"/>
-        <v>6.9669498365818487</v>
+        <v>3.0263131894547879</v>
       </c>
       <c r="E19">
         <v>1.353019</v>
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>11.674188610802952</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0710500000369549</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
       <c r="B20" s="6">
-        <v>17.032720999999999</v>
+        <v>7.2563430000000002</v>
       </c>
       <c r="C20">
         <v>2.413516</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="0"/>
-        <v>7.0572231549324718</v>
+        <v>3.0065443941535919</v>
       </c>
       <c r="E20">
         <v>1.428434</v>
       </c>
       <c r="F20">
         <f t="shared" si="1"/>
-        <v>11.924051793782562</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0799287891495162</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
       <c r="B21" s="6">
-        <v>18.229096999999999</v>
+        <v>7.6664630000000002</v>
       </c>
       <c r="C21">
         <v>2.524848</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" si="0"/>
-        <v>7.2198789788533801</v>
+        <v>3.036405755910851</v>
       </c>
       <c r="E21">
         <v>1.5375620000000001</v>
       </c>
       <c r="F21">
         <f t="shared" si="1"/>
-        <v>11.855845162666609</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9861163322194484</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
       <c r="B22" s="6">
-        <v>19.070878</v>
+        <v>8.0430080000000004</v>
       </c>
       <c r="C22">
         <v>2.716825</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="0"/>
-        <v>7.0195459773816866</v>
+        <v>2.9604439005088663</v>
       </c>
       <c r="E22">
         <v>1.596641</v>
       </c>
       <c r="F22">
         <f t="shared" si="1"/>
-        <v>11.944374471155383</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0374555081574384</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
       <c r="B23" s="6">
-        <v>20.289345000000001</v>
+        <v>8.5758749999999999</v>
       </c>
       <c r="C23">
         <v>2.8388429999999998</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" si="0"/>
-        <v>7.1470472301567938</v>
+        <v>3.0209049954506115</v>
       </c>
       <c r="E23">
         <v>1.672161</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>12.133607350009958</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.1286179979080959</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
       <c r="B24" s="6">
-        <v>20.676687000000001</v>
+        <v>8.9751270000000005</v>
       </c>
       <c r="C24">
         <v>2.9750390000000002</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="0"/>
-        <v>6.9500557807813612</v>
+        <v>3.0168098636690139</v>
       </c>
       <c r="E24">
         <v>1.7628299999999999</v>
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>11.72925750072327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0913173703646981</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
       <c r="B25" s="6">
-        <v>21.899799999999999</v>
+        <v>9.3495889999999999</v>
       </c>
       <c r="C25">
         <v>3.0683389999999999</v>
       </c>
       <c r="D25" s="6">
         <f t="shared" si="0"/>
-        <v>7.1373469489518593</v>
+        <v>3.0471173491586163</v>
       </c>
       <c r="E25">
         <v>1.8428850000000001</v>
       </c>
       <c r="F25">
         <f t="shared" si="1"/>
-        <v>11.88343276981472</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0733436975177506</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
       <c r="B26" s="6">
-        <v>22.377856999999999</v>
+        <v>9.8527170000000002</v>
       </c>
       <c r="C26">
         <v>3.2272479999999999</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="0"/>
-        <v>6.9340369875510026</v>
+        <v>3.0529779552113752</v>
       </c>
       <c r="E26">
         <v>1.928795</v>
       </c>
       <c r="F26">
         <f t="shared" si="1"/>
-        <v>11.601988288024387</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.1082240466197808</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
       <c r="B27" s="6">
-        <v>24.132621</v>
+        <v>10.180562999999999</v>
       </c>
       <c r="C27">
         <v>3.381545</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" si="0"/>
-        <v>7.1365665694231479</v>
+        <v>3.0106247292287991</v>
       </c>
       <c r="E27">
         <v>2.0565920000000002</v>
       </c>
       <c r="F27">
         <f t="shared" si="1"/>
-        <v>11.734277387055867</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9502103479931838</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
       <c r="B28" s="6">
-        <v>24.831582999999998</v>
+        <v>10.700431</v>
       </c>
       <c r="C28">
         <v>3.4923199999999999</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="0"/>
-        <v>7.1103401177440784</v>
+        <v>3.0639892678792324</v>
       </c>
       <c r="E28">
         <v>2.119332</v>
       </c>
       <c r="F28">
         <f t="shared" si="1"/>
-        <v>11.716702715761381</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0489640131890612</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
       <c r="B29" s="6">
-        <v>26.061553</v>
+        <v>11.212687000000001</v>
       </c>
       <c r="C29">
         <v>3.6668919999999998</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="0"/>
-        <v>7.1072594993253144</v>
+        <v>3.0578176286620935</v>
       </c>
       <c r="E29">
         <v>2.2130070000000002</v>
       </c>
       <c r="F29">
         <f t="shared" si="1"/>
-        <v>11.776534371558697</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>5.0667200781561013</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
       <c r="B30" s="6">
-        <v>27.901105000000001</v>
+        <v>11.635517</v>
       </c>
       <c r="C30">
         <v>3.7689819999999998</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" si="0"/>
-        <v>7.4028225658811859</v>
+        <v>3.0871776516841951</v>
       </c>
       <c r="E30">
         <v>2.3499059999999998</v>
       </c>
       <c r="F30">
         <f t="shared" si="1"/>
-        <v>11.873285569720663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.951481889062797</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
       <c r="B31" s="6">
-        <v>28.604783999999999</v>
+        <v>12.220283</v>
       </c>
       <c r="C31">
         <v>4.518008</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" si="0"/>
-        <v>6.3312822819260166</v>
+        <v>2.704794458088609</v>
       </c>
       <c r="E31">
         <v>2.4693049999999999</v>
       </c>
       <c r="F31">
         <f t="shared" si="1"/>
-        <v>11.584143716551823</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4.9488754933068213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
       <c r="B32" s="6">
-        <v>29.860191</v>
+        <v>12.621880000000001</v>
       </c>
       <c r="C32">
         <v>5.2665649999999999</v>
       </c>
       <c r="D32" s="6">
         <f t="shared" si="0"/>
-        <v>5.6697659670012621</v>
+        <v>2.3966057572630359</v>
       </c>
       <c r="E32">
         <v>3.0958739999999998</v>
       </c>
       <c r="F32">
         <f t="shared" si="1"/>
-        <v>9.6451570703458867</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4.0770005497639765</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
       <c r="B33" s="6">
-        <v>30.595779</v>
+        <v>13.593923999999999</v>
       </c>
       <c r="C33">
         <v>4.8746859999999996</v>
       </c>
       <c r="D33" s="6">
         <f t="shared" si="0"/>
-        <v>6.276461499263748</v>
+        <v>2.7886768501601948</v>
       </c>
       <c r="E33">
         <v>3.0987979999999999</v>
       </c>
       <c r="F33">
         <f t="shared" si="1"/>
-        <v>9.8734344736249344</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4.386837735147628</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
       <c r="B34" s="6">
-        <v>30.810445000000001</v>
+        <v>13.916072</v>
       </c>
       <c r="C34">
         <v>4.905627</v>
       </c>
       <c r="D34" s="6">
         <f t="shared" si="0"/>
-        <v>6.2806334440021638</v>
+        <v>2.8367570547047301</v>
       </c>
       <c r="E34">
         <v>3.2922889999999998</v>
       </c>
       <c r="F34">
         <f t="shared" si="1"/>
-        <v>9.3583658664230285</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4.2268682974064555</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
       <c r="B35" s="6">
-        <v>32.276363000000003</v>
+        <v>14.713252000000001</v>
       </c>
       <c r="C35">
         <v>5.2940889999999996</v>
       </c>
       <c r="D35" s="6">
         <f t="shared" si="0"/>
-        <v>6.0966793342537322</v>
+        <v>2.779184860700302</v>
       </c>
       <c r="E35">
         <v>3.4938380000000002</v>
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
-        <v>9.2380823037587891</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4.2112004048270126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B36"/>
       <c r="D36"/>
     </row>
-    <row r="37" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+    <row r="37" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="8"/>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="10"/>
+      <c r="F38" s="7"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>10.818895184135977</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>14.23371806295199</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>16.640132316822125</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>17.288917204180393</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>17.652806202296969</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>16.005305690666784</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>14.711932631747588</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>14.198925579947767</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>16.768739004907282</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>17.351490331321592</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>17.526366779998042</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>14.051095395875574</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>13.550977924932013</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>17.128358094405954</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>17.212800477613261</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>14.545692898728662</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>16.810521577366149</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>17.143905414281694</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>16.572422586055698</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>16.975535320673025</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>15.893741901678764</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>15.904545349482248</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>17.262436277613034</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>16.276120792209106</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>9.1739231638781824</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
@@ -1789,7 +1789,7 @@
         <v>8.0189929709071226</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>9.2479398810376612</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>10.169805003251382</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>16.156568041204466</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>12.520129089553457</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>40000000</v>
       </c>
@@ -1914,23 +1914,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="22.6640625" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="22.6328125" customWidth="1"/>
+    <col min="5" max="5" width="22.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8"/>
@@ -1938,7 +1938,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>2.0506150000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>0.62085500000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>8</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>0.39751399999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>16</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>0.39396199999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>32</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>0.40589199999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>64</v>
       </c>
@@ -2063,21 +2063,21 @@
         <v>0.40879700000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="8"/>
@@ -2085,7 +2085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>1.794886</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>0.43836999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>8</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0.225991</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>0.15532199999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>32</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0.14178299999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>64</v>
       </c>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C4B56E-1352-40AA-98A0-2B0DE9B68D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BA1BAF-E601-47E0-808D-ACCAB26369FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
@@ -1960,14 +1960,15 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <v>4.221819</v>
+        <f>'Testing 1'!$B$5</f>
+        <v>1.981976</v>
       </c>
       <c r="C5">
         <v>1.9988060000000001</v>
       </c>
       <c r="D5" s="6">
         <f>B5/C5</f>
-        <v>2.1121704657680636</v>
+        <v>0.99157997324402658</v>
       </c>
       <c r="E5">
         <v>2.0506150000000001</v>
@@ -1978,14 +1979,15 @@
         <v>4</v>
       </c>
       <c r="B6" s="6">
-        <v>4.221819</v>
+        <f>'Testing 1'!$B$5</f>
+        <v>1.981976</v>
       </c>
       <c r="C6">
         <v>1.163114</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" ref="D6:D10" si="0">B6/C6</f>
-        <v>3.6297551228856331</v>
+        <v>1.7040255727297582</v>
       </c>
       <c r="E6">
         <v>0.62085500000000005</v>
@@ -1996,14 +1998,15 @@
         <v>8</v>
       </c>
       <c r="B7" s="6">
-        <v>4.221819</v>
+        <f>'Testing 1'!$B$5</f>
+        <v>1.981976</v>
       </c>
       <c r="C7">
         <v>0.66360600000000003</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="0"/>
-        <v>6.3619361488594128</v>
+        <v>2.9866758287296977</v>
       </c>
       <c r="E7">
         <v>0.39751399999999998</v>
@@ -2014,14 +2017,15 @@
         <v>16</v>
       </c>
       <c r="B8" s="6">
-        <v>4.221819</v>
+        <f>'Testing 1'!$B$5</f>
+        <v>1.981976</v>
       </c>
       <c r="C8">
         <v>0.445718</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="0"/>
-        <v>9.4719508747683516</v>
+        <v>4.4467039697746111</v>
       </c>
       <c r="E8">
         <v>0.39396199999999998</v>
@@ -2032,14 +2036,15 @@
         <v>32</v>
       </c>
       <c r="B9" s="6">
-        <v>4.221819</v>
+        <f>'Testing 1'!$B$5</f>
+        <v>1.981976</v>
       </c>
       <c r="C9">
         <v>0.44677899999999998</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="0"/>
-        <v>9.4494571141436818</v>
+        <v>4.4361440443709306</v>
       </c>
       <c r="E9">
         <v>0.40589199999999998</v>
@@ -2050,14 +2055,15 @@
         <v>64</v>
       </c>
       <c r="B10" s="6">
-        <v>4.221819</v>
+        <f>'Testing 1'!$B$5</f>
+        <v>1.981976</v>
       </c>
       <c r="C10">
         <v>0.44517200000000001</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v>9.4835681489401846</v>
+        <v>4.4521578176525027</v>
       </c>
       <c r="E10">
         <v>0.40879700000000002</v>
@@ -2107,14 +2113,15 @@
         <v>1</v>
       </c>
       <c r="B16" s="6">
-        <v>1.819431</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>1.909535</v>
       </c>
       <c r="C16">
         <v>1.7803150000000001</v>
       </c>
       <c r="D16" s="6">
         <f>B16/C16</f>
-        <v>1.0219713927029768</v>
+        <v>1.0725826609335987</v>
       </c>
       <c r="E16">
         <v>1.794886</v>
@@ -2125,14 +2132,15 @@
         <v>4</v>
       </c>
       <c r="B17" s="6">
-        <v>1.819431</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>1.909535</v>
       </c>
       <c r="C17">
         <v>0.91214399999999995</v>
       </c>
       <c r="D17" s="6">
         <f t="shared" ref="D17:D21" si="1">B17/C17</f>
-        <v>1.9946751828658633</v>
+        <v>2.0934578312196321</v>
       </c>
       <c r="E17">
         <v>0.43836999999999998</v>
@@ -2143,14 +2151,15 @@
         <v>8</v>
       </c>
       <c r="B18" s="6">
-        <v>1.819431</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>1.909535</v>
       </c>
       <c r="C18">
         <v>0.41222500000000001</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="1"/>
-        <v>4.4136842743647282</v>
+        <v>4.6322639335314451</v>
       </c>
       <c r="E18">
         <v>0.225991</v>
@@ -2161,14 +2170,15 @@
         <v>16</v>
       </c>
       <c r="B19" s="6">
-        <v>1.819431</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>1.909535</v>
       </c>
       <c r="C19">
         <v>0.248222</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="1"/>
-        <v>7.3298539210867695</v>
+        <v>7.6928515602968313</v>
       </c>
       <c r="E19">
         <v>0.15532199999999999</v>
@@ -2179,14 +2189,15 @@
         <v>32</v>
       </c>
       <c r="B20" s="6">
-        <v>1.819431</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>1.909535</v>
       </c>
       <c r="C20">
         <v>0.18618000000000001</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="1"/>
-        <v>9.7724299065420563</v>
+        <v>10.256391663981093</v>
       </c>
       <c r="E20">
         <v>0.14178299999999999</v>
@@ -2197,14 +2208,15 @@
         <v>64</v>
       </c>
       <c r="B21" s="6">
-        <v>1.819431</v>
+        <f>'Testing 1'!$B$40</f>
+        <v>1.909535</v>
       </c>
       <c r="C21">
         <v>0.175349</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" si="1"/>
-        <v>10.376055751672379</v>
+        <v>10.889910977536227</v>
       </c>
       <c r="E21">
         <v>0.141709</v>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BA1BAF-E601-47E0-808D-ACCAB26369FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chtay\Documents\FIT3143\FIT3143_lab01\graph\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BA1BAF-E601-47E0-808D-ACCAB26369FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9952CFA0-98CA-4E14-A017-A57F195CD15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Testing 2" sheetId="2" r:id="rId2"/>
+    <sheet name="task1 optimise and unoptimise" sheetId="3" r:id="rId2"/>
+    <sheet name="Testing 2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>n</t>
   </si>
@@ -74,6 +75,24 @@
   <si>
     <t>Open MP</t>
   </si>
+  <si>
+    <t>Before Optimise</t>
+  </si>
+  <si>
+    <t>After optimise</t>
+  </si>
+  <si>
+    <t>Speed up</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
 </sst>
 </file>
 
@@ -96,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -122,11 +141,109 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -142,23 +259,192 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -169,6 +455,1421 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-MY"/>
+              <a:t>Comparison before and after optimise TASK1</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11562575266327005"/>
+          <c:y val="0.16263932224094446"/>
+          <c:w val="0.81574679635633784"/>
+          <c:h val="0.65510337448665146"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'task1 optimise and unoptimise'!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Before Optimise</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'task1 optimise and unoptimise'!$B$7:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>10000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'task1 optimise and unoptimise'!$C$7:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.778915</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.2206219999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.102762</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.203678</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.911546000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.685684999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26.964960999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D1CA-4EA4-B7FB-1700C8A0A7D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'task1 optimise and unoptimise'!$D$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>After optimise</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'task1 optimise and unoptimise'!$B$7:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>10000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'task1 optimise and unoptimise'!$D$7:$D$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.909535</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.935181</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.8301439999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5089629999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8258559999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.2858409999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.736215</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D1CA-4EA4-B7FB-1700C8A0A7D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="373488240"/>
+        <c:axId val="71420656"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="373488240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="71420656"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="71420656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="373488240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="236">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ADEB1D2-1C61-0CFA-5125-C6DDF0CA84D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2110740" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{009C310D-F73A-38A4-F802-606A09BB43C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8191500" y="6469380"/>
+          <a:ext cx="2110740" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-MY" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>number of n</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>517529</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>141668</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="264560" cy="1794787"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07A51608-8C72-6D59-095D-79DD469A558B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="4842575" y="4564382"/>
+          <a:ext cx="1794787" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>computation time in second</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-MY" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{35761736-ECE1-4136-A04C-E7A6A5C01A11}" name="Table1" displayName="Table1" ref="B5:E14" totalsRowCount="1" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="B5:E13" xr:uid="{35761736-ECE1-4136-A04C-E7A6A5C01A11}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{4A5BEC9D-21BB-41AB-8175-8B2FB98605EB}" name="Column1" dataDxfId="7" totalsRowDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{3FC5512B-02EF-47A2-B959-FB8FEDE3F971}" name="Computational Time (sec)" dataDxfId="6" totalsRowDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{51B9DD5E-C61B-4C00-89B7-1D3A63DF34BF}" name="Column2" dataDxfId="5" totalsRowDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{8A94D6B7-909A-41AE-A94D-903BA8ADEECB}" name="Column3" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="0">
+      <calculatedColumnFormula>C6/D6</calculatedColumnFormula>
+      <totalsRowFormula>AVERAGE(E7:E13)</totalsRowFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,37 +2136,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.6328125" customWidth="1"/>
-    <col min="2" max="2" width="22.6328125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="22.6328125" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6328125" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="4"/>
       <c r="D1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -485,7 +2186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>10000000</v>
       </c>
@@ -507,7 +2208,7 @@
         <v>5.0296300055829057</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>11000000</v>
       </c>
@@ -529,7 +2230,7 @@
         <v>5.0123139587421681</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>12000000</v>
       </c>
@@ -551,7 +2252,7 @@
         <v>5.015924723818598</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>13000000</v>
       </c>
@@ -573,7 +2274,7 @@
         <v>5.1652234884794268</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>14000000</v>
       </c>
@@ -595,7 +2296,7 @@
         <v>4.9647238977675521</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>15000000</v>
       </c>
@@ -617,7 +2318,7 @@
         <v>4.909989127499311</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>16000000</v>
       </c>
@@ -639,7 +2340,7 @@
         <v>5.0517743163434181</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>17000000</v>
       </c>
@@ -661,7 +2362,7 @@
         <v>4.9751176818027245</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>18000000</v>
       </c>
@@ -683,7 +2384,7 @@
         <v>4.9432804031899931</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>19000000</v>
       </c>
@@ -705,7 +2406,7 @@
         <v>5.08744203799316</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>20000000</v>
       </c>
@@ -727,7 +2428,7 @@
         <v>5.0664287302453568</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>21000000</v>
       </c>
@@ -749,7 +2450,7 @@
         <v>5.0355031023482457</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>22000000</v>
       </c>
@@ -771,7 +2472,7 @@
         <v>4.9781198265015565</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>23000000</v>
       </c>
@@ -793,7 +2494,7 @@
         <v>5.0012124635906865</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>24000000</v>
       </c>
@@ -815,7 +2516,7 @@
         <v>5.0710500000369549</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>25000000</v>
       </c>
@@ -837,7 +2538,7 @@
         <v>5.0799287891495162</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>26000000</v>
       </c>
@@ -859,7 +2560,7 @@
         <v>4.9861163322194484</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>27000000</v>
       </c>
@@ -881,7 +2582,7 @@
         <v>5.0374555081574384</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>28000000</v>
       </c>
@@ -903,7 +2604,7 @@
         <v>5.1286179979080959</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>29000000</v>
       </c>
@@ -925,7 +2626,7 @@
         <v>5.0913173703646981</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>30000000</v>
       </c>
@@ -947,7 +2648,7 @@
         <v>5.0733436975177506</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>31000000</v>
       </c>
@@ -969,7 +2670,7 @@
         <v>5.1082240466197808</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>32000000</v>
       </c>
@@ -991,7 +2692,7 @@
         <v>4.9502103479931838</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>33000000</v>
       </c>
@@ -1013,7 +2714,7 @@
         <v>5.0489640131890612</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>34000000</v>
       </c>
@@ -1035,7 +2736,7 @@
         <v>5.0667200781561013</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>35000000</v>
       </c>
@@ -1057,7 +2758,7 @@
         <v>4.951481889062797</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>36000000</v>
       </c>
@@ -1079,7 +2780,7 @@
         <v>4.9488754933068213</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>37000000</v>
       </c>
@@ -1101,7 +2802,7 @@
         <v>4.0770005497639765</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>38000000</v>
       </c>
@@ -1123,7 +2824,7 @@
         <v>4.386837735147628</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>39000000</v>
       </c>
@@ -1145,7 +2846,7 @@
         <v>4.2268682974064555</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>40000000</v>
       </c>
@@ -1167,37 +2868,37 @@
         <v>4.2112004048270126</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B36"/>
       <c r="D36"/>
     </row>
-    <row r="37" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="8"/>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="7"/>
+      <c r="F38" s="10"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +2918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>10000000</v>
       </c>
@@ -1228,7 +2929,7 @@
         <v>0.19961499999999999</v>
       </c>
       <c r="D40" s="6">
-        <f t="shared" ref="D40:D70" si="2">B40/C40</f>
+        <f>B40/C40</f>
         <v>9.5660897227162298</v>
       </c>
       <c r="E40">
@@ -1239,7 +2940,7 @@
         <v>10.818895184135977</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>11000000</v>
       </c>
@@ -1250,7 +2951,7 @@
         <v>0.208622</v>
       </c>
       <c r="D41" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D40:D70" si="2">B41/C41</f>
         <v>9.877745395979332</v>
       </c>
       <c r="E41">
@@ -1261,7 +2962,7 @@
         <v>14.23371806295199</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>12000000</v>
       </c>
@@ -1283,7 +2984,7 @@
         <v>16.640132316822125</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>13000000</v>
       </c>
@@ -1305,7 +3006,7 @@
         <v>17.288917204180393</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>14000000</v>
       </c>
@@ -1327,7 +3028,7 @@
         <v>17.652806202296969</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>15000000</v>
       </c>
@@ -1349,7 +3050,7 @@
         <v>16.005305690666784</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>16000000</v>
       </c>
@@ -1371,7 +3072,7 @@
         <v>14.711932631747588</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>17000000</v>
       </c>
@@ -1393,7 +3094,7 @@
         <v>14.198925579947767</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>18000000</v>
       </c>
@@ -1415,7 +3116,7 @@
         <v>16.768739004907282</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>19000000</v>
       </c>
@@ -1437,7 +3138,7 @@
         <v>17.351490331321592</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>20000000</v>
       </c>
@@ -1459,7 +3160,7 @@
         <v>17.526366779998042</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>21000000</v>
       </c>
@@ -1481,7 +3182,7 @@
         <v>14.051095395875574</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>22000000</v>
       </c>
@@ -1503,7 +3204,7 @@
         <v>13.550977924932013</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>23000000</v>
       </c>
@@ -1525,7 +3226,7 @@
         <v>17.128358094405954</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>24000000</v>
       </c>
@@ -1547,7 +3248,7 @@
         <v>17.212800477613261</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>25000000</v>
       </c>
@@ -1569,7 +3270,7 @@
         <v>14.545692898728662</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>26000000</v>
       </c>
@@ -1591,7 +3292,7 @@
         <v>16.810521577366149</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>27000000</v>
       </c>
@@ -1613,7 +3314,7 @@
         <v>17.143905414281694</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>28000000</v>
       </c>
@@ -1635,7 +3336,7 @@
         <v>16.572422586055698</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>29000000</v>
       </c>
@@ -1657,7 +3358,7 @@
         <v>16.975535320673025</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>30000000</v>
       </c>
@@ -1679,7 +3380,7 @@
         <v>15.893741901678764</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>31000000</v>
       </c>
@@ -1701,7 +3402,7 @@
         <v>15.904545349482248</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>32000000</v>
       </c>
@@ -1723,7 +3424,7 @@
         <v>17.262436277613034</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>33000000</v>
       </c>
@@ -1745,7 +3446,7 @@
         <v>16.276120792209106</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>34000000</v>
       </c>
@@ -1767,7 +3468,7 @@
         <v>9.1739231638781824</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>35000000</v>
       </c>
@@ -1789,7 +3490,7 @@
         <v>8.0189929709071226</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>36000000</v>
       </c>
@@ -1811,7 +3512,7 @@
         <v>9.2479398810376612</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>37000000</v>
       </c>
@@ -1833,7 +3534,7 @@
         <v>10.169805003251382</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>38000000</v>
       </c>
@@ -1855,7 +3556,7 @@
         <v>16.156568041204466</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>39000000</v>
       </c>
@@ -1877,7 +3578,7 @@
         <v>12.520129089553457</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>40000000</v>
       </c>
@@ -1912,25 +3613,190 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C158EF-9F72-4F28-8328-C1577C962B46}">
+  <dimension ref="B5:E15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="31.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="13">
+        <v>10000000</v>
+      </c>
+      <c r="C7" s="11">
+        <v>3.778915</v>
+      </c>
+      <c r="D7" s="11">
+        <v>1.909535</v>
+      </c>
+      <c r="E7" s="14">
+        <f>C7/D7</f>
+        <v>1.9789713202428865</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="13">
+        <v>15000000</v>
+      </c>
+      <c r="C8" s="11">
+        <v>6.2206219999999997</v>
+      </c>
+      <c r="D8" s="11">
+        <v>2.935181</v>
+      </c>
+      <c r="E8" s="14">
+        <f t="shared" ref="E8:E13" si="0">C8/D8</f>
+        <v>2.1193316528009687</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="13">
+        <v>20000000</v>
+      </c>
+      <c r="C9" s="11">
+        <v>10.102762</v>
+      </c>
+      <c r="D9" s="11">
+        <v>4.8301439999999998</v>
+      </c>
+      <c r="E9" s="14">
+        <f>C9/D9</f>
+        <v>2.0916067926753326</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="13">
+        <v>25000000</v>
+      </c>
+      <c r="C10" s="11">
+        <v>13.203678</v>
+      </c>
+      <c r="D10" s="11">
+        <v>5.5089629999999996</v>
+      </c>
+      <c r="E10" s="14">
+        <f t="shared" si="0"/>
+        <v>2.3967628753360661</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="13">
+        <v>30000000</v>
+      </c>
+      <c r="C11" s="11">
+        <v>17.911546000000001</v>
+      </c>
+      <c r="D11" s="11">
+        <v>7.8258559999999999</v>
+      </c>
+      <c r="E11" s="14">
+        <f t="shared" si="0"/>
+        <v>2.288765088445277</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="13">
+        <v>35000000</v>
+      </c>
+      <c r="C12" s="11">
+        <v>19.685684999999999</v>
+      </c>
+      <c r="D12" s="11">
+        <v>8.2858409999999996</v>
+      </c>
+      <c r="E12" s="14">
+        <f t="shared" si="0"/>
+        <v>2.3758222007880674</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="20">
+        <v>40000000</v>
+      </c>
+      <c r="C13" s="21">
+        <v>26.964960999999999</v>
+      </c>
+      <c r="D13" s="21">
+        <v>11.736215</v>
+      </c>
+      <c r="E13" s="22">
+        <f t="shared" si="0"/>
+        <v>2.2975858059860013</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22">
+        <f>AVERAGE(E7:E13)</f>
+        <v>2.2212636766106568</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D2B590C-628F-42C3-BA14-2549B4CA5D44}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="22.6328125" customWidth="1"/>
-    <col min="5" max="5" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8"/>
@@ -1938,7 +3804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1955,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1974,7 +3840,7 @@
         <v>2.0506150000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1993,7 +3859,7 @@
         <v>0.62085500000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>8</v>
       </c>
@@ -2012,7 +3878,7 @@
         <v>0.39751399999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>16</v>
       </c>
@@ -2031,7 +3897,7 @@
         <v>0.39396199999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>32</v>
       </c>
@@ -2050,7 +3916,7 @@
         <v>0.40589199999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>64</v>
       </c>
@@ -2069,21 +3935,21 @@
         <v>0.40879700000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="8"/>
@@ -2091,7 +3957,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -2108,7 +3974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -2127,7 +3993,7 @@
         <v>1.794886</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>4</v>
       </c>
@@ -2146,7 +4012,7 @@
         <v>0.43836999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>8</v>
       </c>
@@ -2165,7 +4031,7 @@
         <v>0.225991</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -2184,7 +4050,7 @@
         <v>0.15532199999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>32</v>
       </c>
@@ -2203,7 +4069,7 @@
         <v>0.14178299999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>64</v>
       </c>

--- a/graph/RunningTimeRecord.xlsx
+++ b/graph/RunningTimeRecord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MONASH\Year_3_sem_1\FIT3143\Week 04\FIT3143_lab01\graph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9952CFA0-98CA-4E14-A017-A57F195CD15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7EFC62-0C2E-4E3B-BAA1-7288FF0E9D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -259,6 +259,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -271,22 +286,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -298,47 +297,6 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -362,6 +320,20 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -380,6 +352,20 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -395,6 +381,19 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -423,13 +422,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -439,6 +431,13 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -478,13 +477,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -512,13 +509,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -561,19 +556,13 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
+            <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:miter lim="800000"/>
             </a:ln>
-            <a:effectLst>
-              <a:glow rad="139700">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="175000"/>
-                  <a:alpha val="14000"/>
-                </a:schemeClr>
-              </a:glow>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -587,17 +576,17 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:ln>
-                      <a:noFill/>
-                    </a:ln>
                     <a:solidFill>
-                      <a:schemeClr val="lt1">
+                      <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -623,11 +612,11 @@
                   <c:spPr>
                     <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="50000"/>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -717,19 +706,13 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
+            <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
+              <a:miter lim="800000"/>
             </a:ln>
-            <a:effectLst>
-              <a:glow rad="139700">
-                <a:schemeClr val="accent2">
-                  <a:satMod val="175000"/>
-                  <a:alpha val="14000"/>
-                </a:schemeClr>
-              </a:glow>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -743,17 +726,17 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:ln>
-                      <a:noFill/>
-                    </a:ln>
                     <a:solidFill>
-                      <a:schemeClr val="lt1">
+                      <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -779,11 +762,11 @@
                   <c:spPr>
                     <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="50000"/>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -881,23 +864,13 @@
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                  <a:alpha val="32000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -909,8 +882,15 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:tailEnd type="none" w="med" len="lg"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -920,12 +900,10 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="75000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -953,23 +931,13 @@
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                  <a:alpha val="32000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -981,8 +949,15 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:tailEnd type="none" w="med" len="lg"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -992,12 +967,10 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="75000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1036,12 +1009,10 @@
         <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="75000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1059,14 +1030,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
+        <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1080,11 +1048,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </a:defRPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -1138,46 +1102,57 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="236">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="237">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:tailEnd type="none" w="med" len="lg"/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
+        <a:schemeClr val="bg1"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1192,8 +1167,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
+      <a:schemeClr val="tx1">
         <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1203,18 +1179,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="15000"/>
-        <a:lumOff val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -1222,90 +1203,51 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:miter lim="800000"/>
-      </a:ln>
-      <a:effectLst>
-        <a:glow rad="63500">
-          <a:schemeClr val="phClr">
-            <a:satMod val="175000"/>
-            <a:alpha val="25000"/>
-          </a:schemeClr>
-        </a:glow>
-      </a:effectLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
     </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
+    <cs:lnRef idx="0"/>
     <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:miter lim="800000"/>
-      </a:ln>
-      <a:effectLst>
-        <a:glow rad="63500">
-          <a:schemeClr val="phClr">
-            <a:satMod val="175000"/>
-            <a:alpha val="25000"/>
-          </a:schemeClr>
-        </a:glow>
-      </a:effectLst>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="22225" cap="rnd">
+      <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:miter lim="800000"/>
       </a:ln>
-      <a:effectLst>
-        <a:glow rad="139700">
-          <a:schemeClr val="phClr">
-            <a:satMod val="175000"/>
-            <a:alpha val="14000"/>
-          </a:schemeClr>
-        </a:glow>
-      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
@@ -1315,30 +1257,23 @@
     <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:effectRef>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:lumMod val="60000"/>
-          <a:lumOff val="40000"/>
-        </a:schemeClr>
+        <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:effectLst>
-        <a:glow rad="63500">
-          <a:schemeClr val="phClr">
-            <a:satMod val="175000"/>
-            <a:alpha val="25000"/>
-          </a:schemeClr>
-        </a:glow>
-      </a:effectLst>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -1346,7 +1281,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1362,16 +1297,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -1383,22 +1319,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1407,16 +1343,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -1425,16 +1361,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:errorBar>
@@ -1443,7 +1379,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -1451,27 +1387,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="65000"/>
-                <a:lumOff val="35000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="32000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -1481,30 +1407,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
-                <a:alpha val="25000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="65000"/>
-                <a:lumOff val="35000"/>
-                <a:alpha val="25000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+            <a:alpha val="32000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -1513,16 +1426,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:schemeClr val="tx1"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -1531,16 +1441,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -1549,26 +1459,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1576,10 +1487,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:tailEnd type="none" w="med" len="lg"/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1587,16 +1508,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -1605,11 +1526,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1618,16 +1540,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="25400" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
+      <a:ln w="12700" cap="rnd"/>
     </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
@@ -1635,8 +1551,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1646,21 +1563,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1669,10 +1584,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="75000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:tailEnd type="none" w="med" len="lg"/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1680,7 +1608,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -1776,7 +1704,7 @@
           <a:r>
             <a:rPr lang="en-MY" sz="1100" b="1">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
             <a:t>number of n</a:t>
@@ -1789,11 +1717,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>517529</xdr:colOff>
+      <xdr:colOff>517534</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>141668</xdr:rowOff>
+      <xdr:rowOff>124805</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="264560" cy="1794787"/>
+    <xdr:ext cx="264560" cy="1828514"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="7" name="TextBox 6">
@@ -1807,8 +1735,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="5400000">
-          <a:off x="4842575" y="4564382"/>
-          <a:ext cx="1794787" cy="264560"/>
+          <a:off x="4825717" y="4564382"/>
+          <a:ext cx="1828514" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1836,16 +1764,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100">
+            <a:rPr lang="en-US" sz="1100" b="1">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
             <a:t>computation time in second</a:t>
           </a:r>
-          <a:endParaRPr lang="en-MY" sz="1100">
+          <a:endParaRPr lang="en-MY" sz="1100" b="1">
             <a:solidFill>
-              <a:schemeClr val="bg1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
           </a:endParaRPr>
         </a:p>
@@ -1857,13 +1785,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{35761736-ECE1-4136-A04C-E7A6A5C01A11}" name="Table1" displayName="Table1" ref="B5:E14" totalsRowCount="1" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{35761736-ECE1-4136-A04C-E7A6A5C01A11}" name="Table1" displayName="Table1" ref="B5:E14" totalsRowCount="1" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="B5:E13" xr:uid="{35761736-ECE1-4136-A04C-E7A6A5C01A11}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4A5BEC9D-21BB-41AB-8175-8B2FB98605EB}" name="Column1" dataDxfId="7" totalsRowDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{3FC5512B-02EF-47A2-B959-FB8FEDE3F971}" name="Computational Time (sec)" dataDxfId="6" totalsRowDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{51B9DD5E-C61B-4C00-89B7-1D3A63DF34BF}" name="Column2" dataDxfId="5" totalsRowDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{8A94D6B7-909A-41AE-A94D-903BA8ADEECB}" name="Column3" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{4A5BEC9D-21BB-41AB-8175-8B2FB98605EB}" name="Column1" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3FC5512B-02EF-47A2-B959-FB8FEDE3F971}" name="Computational Time (sec)" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{51B9DD5E-C61B-4C00-89B7-1D3A63DF34BF}" name="Column2" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{8A94D6B7-909A-41AE-A94D-903BA8ADEECB}" name="Column3" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>C6/D6</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(E7:E13)</totalsRowFormula>
     </tableColumn>
@@ -2157,14 +2085,14 @@
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -2873,29 +2801,29 @@
       <c r="D36"/>
     </row>
     <row r="37" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B38" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="10" t="s">
+      <c r="D38" s="19"/>
+      <c r="E38" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="10"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -2951,7 +2879,7 @@
         <v>0.208622</v>
       </c>
       <c r="D41" s="6">
-        <f t="shared" ref="D40:D70" si="2">B41/C41</f>
+        <f t="shared" ref="D41:D70" si="2">B41/C41</f>
         <v>9.877745395979332</v>
       </c>
       <c r="E41">
@@ -3617,150 +3545,150 @@
   <dimension ref="B5:E15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.88671875" customWidth="1"/>
     <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13">
+      <c r="B7" s="9">
         <v>10000000</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="7">
         <v>3.778915</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="7">
         <v>1.909535</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="10">
         <f>C7/D7</f>
         <v>1.9789713202428865</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="13">
+      <c r="B8" s="9">
         <v>15000000</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="7">
         <v>6.2206219999999997</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="7">
         <v>2.935181</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="10">
         <f t="shared" ref="E8:E13" si="0">C8/D8</f>
         <v>2.1193316528009687</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="13">
+      <c r="B9" s="9">
         <v>20000000</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="7">
         <v>10.102762</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="7">
         <v>4.8301439999999998</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="10">
         <f>C9/D9</f>
         <v>2.0916067926753326</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="13">
+      <c r="B10" s="9">
         <v>25000000</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="7">
         <v>13.203678</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="7">
         <v>5.5089629999999996</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="10">
         <f t="shared" si="0"/>
         <v>2.3967628753360661</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="13">
+      <c r="B11" s="9">
         <v>30000000</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="7">
         <v>17.911546000000001</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="7">
         <v>7.8258559999999999</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="10">
         <f t="shared" si="0"/>
         <v>2.288765088445277</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="13">
+      <c r="B12" s="9">
         <v>35000000</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="7">
         <v>19.685684999999999</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="7">
         <v>8.2858409999999996</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="10">
         <f t="shared" si="0"/>
         <v>2.3758222007880674</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="20">
+      <c r="B13" s="15">
         <v>40000000</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="16">
         <v>26.964960999999999</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="16">
         <v>11.736215</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="17">
         <f t="shared" si="0"/>
         <v>2.2975858059860013</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17">
         <f>AVERAGE(E7:E13)</f>
         <v>2.2212636766106568</v>
       </c>
@@ -3796,10 +3724,10 @@
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
@@ -3949,10 +3877,10 @@
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
